--- a/research/traditional_assets/database/data/south_africa/south_africa_computers_peripherals.xlsx
+++ b/research/traditional_assets/database/data/south_africa/south_africa_computers_peripherals.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1498843466873953</v>
+        <v>0.1495125089513393</v>
       </c>
       <c r="C2">
-        <v>151.1913023313454</v>
+        <v>150.0628489947879</v>
       </c>
       <c r="D2">
-        <v>134.5913023313454</v>
+        <v>135.0738489947879</v>
       </c>
       <c r="E2">
-        <v>-115.5</v>
+        <v>-113.889</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>1.611</v>
       </c>
       <c r="G2">
         <v>16.6</v>
@@ -1451,28 +1451,28 @@
         <v>23.36666666666667</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.0810333</v>
       </c>
       <c r="N2">
-        <v>23.36666666666667</v>
+        <v>23.28563336666667</v>
       </c>
       <c r="O2">
-        <v>6.309</v>
+        <v>6.287121009</v>
       </c>
       <c r="P2">
-        <v>17.05766666666667</v>
+        <v>16.99851235766667</v>
       </c>
       <c r="Q2">
-        <v>18.35766666666667</v>
+        <v>18.29851235766667</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1498843466873953</v>
+        <v>0.1506518373245851</v>
       </c>
       <c r="T2">
-        <v>1.246903653332528</v>
+        <v>1.256097993402555</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>288.3588187407728</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1495125089513393</v>
+        <v>0.1491406712152833</v>
       </c>
       <c r="C3">
-        <v>150.0628489947879</v>
+        <v>148.937868232131</v>
       </c>
       <c r="D3">
-        <v>135.0738489947879</v>
+        <v>135.559868232131</v>
       </c>
       <c r="E3">
-        <v>-113.889</v>
+        <v>-112.278</v>
       </c>
       <c r="F3">
-        <v>1.611</v>
+        <v>3.222</v>
       </c>
       <c r="G3">
         <v>16.6</v>
@@ -1533,28 +1533,28 @@
         <v>23.36666666666667</v>
       </c>
       <c r="M3">
-        <v>0.0810333</v>
+        <v>0.1620666</v>
       </c>
       <c r="N3">
-        <v>23.28563336666667</v>
+        <v>23.20460006666667</v>
       </c>
       <c r="O3">
-        <v>6.287121009</v>
+        <v>6.265242018</v>
       </c>
       <c r="P3">
-        <v>16.99851235766667</v>
+        <v>16.93935804866667</v>
       </c>
       <c r="Q3">
-        <v>18.29851235766667</v>
+        <v>18.23935804866667</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1506518373245851</v>
+        <v>0.1514349910360034</v>
       </c>
       <c r="T3">
-        <v>1.256097993402555</v>
+        <v>1.265479973065849</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>288.3588187407728</v>
+        <v>144.1794093703864</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1491406712152833</v>
+        <v>0.1487688334792273</v>
       </c>
       <c r="C4">
-        <v>148.937868232131</v>
+        <v>147.8163976635162</v>
       </c>
       <c r="D4">
-        <v>135.559868232131</v>
+        <v>136.0493976635162</v>
       </c>
       <c r="E4">
-        <v>-112.278</v>
+        <v>-110.667</v>
       </c>
       <c r="F4">
-        <v>3.222</v>
+        <v>4.833</v>
       </c>
       <c r="G4">
         <v>16.6</v>
@@ -1615,28 +1615,28 @@
         <v>23.36666666666667</v>
       </c>
       <c r="M4">
-        <v>0.1620666</v>
+        <v>0.2430999</v>
       </c>
       <c r="N4">
-        <v>23.20460006666667</v>
+        <v>23.12356676666667</v>
       </c>
       <c r="O4">
-        <v>6.265242018</v>
+        <v>6.243363027</v>
       </c>
       <c r="P4">
-        <v>16.93935804866667</v>
+        <v>16.88020373966667</v>
       </c>
       <c r="Q4">
-        <v>18.23935804866667</v>
+        <v>18.18020373966667</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1514349910360034</v>
+        <v>0.1522342922466261</v>
       </c>
       <c r="T4">
-        <v>1.265479973065849</v>
+        <v>1.275055395608798</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>144.1794093703864</v>
+        <v>96.11960624692428</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1487688334792273</v>
+        <v>0.1483969957431714</v>
       </c>
       <c r="C5">
-        <v>147.8163976635162</v>
+        <v>146.6984754544645</v>
       </c>
       <c r="D5">
-        <v>136.0493976635162</v>
+        <v>136.5424754544645</v>
       </c>
       <c r="E5">
-        <v>-110.667</v>
+        <v>-109.056</v>
       </c>
       <c r="F5">
-        <v>4.833</v>
+        <v>6.444000000000001</v>
       </c>
       <c r="G5">
         <v>16.6</v>
@@ -1697,28 +1697,28 @@
         <v>23.36666666666667</v>
       </c>
       <c r="M5">
-        <v>0.2430999</v>
+        <v>0.3241332</v>
       </c>
       <c r="N5">
-        <v>23.12356676666667</v>
+        <v>23.04253346666667</v>
       </c>
       <c r="O5">
-        <v>6.243363027</v>
+        <v>6.221484036000001</v>
       </c>
       <c r="P5">
-        <v>16.88020373966667</v>
+        <v>16.82104943066667</v>
       </c>
       <c r="Q5">
-        <v>18.18020373966667</v>
+        <v>18.12104943066667</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1522342922466261</v>
+        <v>0.1530502455658035</v>
       </c>
       <c r="T5">
-        <v>1.275055395608798</v>
+        <v>1.284830306121392</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>96.11960624692428</v>
+        <v>72.08970468519321</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1483969957431714</v>
+        <v>0.1480251580071154</v>
       </c>
       <c r="C6">
-        <v>146.6984754544645</v>
+        <v>145.5841403257962</v>
       </c>
       <c r="D6">
-        <v>136.5424754544645</v>
+        <v>137.0391403257962</v>
       </c>
       <c r="E6">
-        <v>-109.056</v>
+        <v>-107.445</v>
       </c>
       <c r="F6">
-        <v>6.444000000000001</v>
+        <v>8.055000000000001</v>
       </c>
       <c r="G6">
         <v>16.6</v>
@@ -1779,28 +1779,28 @@
         <v>23.36666666666667</v>
       </c>
       <c r="M6">
-        <v>0.3241332</v>
+        <v>0.4051665</v>
       </c>
       <c r="N6">
-        <v>23.04253346666667</v>
+        <v>22.96150016666667</v>
       </c>
       <c r="O6">
-        <v>6.221484036000001</v>
+        <v>6.199605045</v>
       </c>
       <c r="P6">
-        <v>16.82104943066667</v>
+        <v>16.76189512166667</v>
       </c>
       <c r="Q6">
-        <v>18.12104943066667</v>
+        <v>18.06189512166667</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1530502455658035</v>
+        <v>0.1538833768495952</v>
       </c>
       <c r="T6">
-        <v>1.284830306121392</v>
+        <v>1.294811004223725</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>72.08970468519321</v>
+        <v>57.67176374815456</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1480251580071154</v>
+        <v>0.1476533202710595</v>
       </c>
       <c r="C7">
-        <v>145.5841403257962</v>
+        <v>144.4734315637666</v>
       </c>
       <c r="D7">
-        <v>137.0391403257962</v>
+        <v>137.5394315637666</v>
       </c>
       <c r="E7">
-        <v>-107.445</v>
+        <v>-105.834</v>
       </c>
       <c r="F7">
-        <v>8.055000000000001</v>
+        <v>9.666000000000002</v>
       </c>
       <c r="G7">
         <v>16.6</v>
@@ -1861,28 +1861,28 @@
         <v>23.36666666666667</v>
       </c>
       <c r="M7">
-        <v>0.4051665</v>
+        <v>0.4861998000000001</v>
       </c>
       <c r="N7">
-        <v>22.96150016666667</v>
+        <v>22.88046686666667</v>
       </c>
       <c r="O7">
-        <v>6.199605045</v>
+        <v>6.177726054</v>
       </c>
       <c r="P7">
-        <v>16.76189512166667</v>
+        <v>16.70274081266666</v>
       </c>
       <c r="Q7">
-        <v>18.06189512166667</v>
+        <v>18.00274081266667</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1538833768495952</v>
+        <v>0.1547342343309143</v>
       </c>
       <c r="T7">
-        <v>1.294811004223725</v>
+        <v>1.305004057604831</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>57.67176374815456</v>
+        <v>48.05980312346213</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1476533202710595</v>
+        <v>0.1472814825350035</v>
       </c>
       <c r="C8">
-        <v>144.4734315637666</v>
+        <v>143.3663890304251</v>
       </c>
       <c r="D8">
-        <v>137.5394315637666</v>
+        <v>138.0433890304251</v>
       </c>
       <c r="E8">
-        <v>-105.834</v>
+        <v>-104.223</v>
       </c>
       <c r="F8">
-        <v>9.666</v>
+        <v>11.277</v>
       </c>
       <c r="G8">
         <v>16.6</v>
@@ -1943,28 +1943,28 @@
         <v>23.36666666666667</v>
       </c>
       <c r="M8">
-        <v>0.4861998</v>
+        <v>0.5672331</v>
       </c>
       <c r="N8">
-        <v>22.88046686666667</v>
+        <v>22.79943356666667</v>
       </c>
       <c r="O8">
-        <v>6.177726054</v>
+        <v>6.155847063</v>
       </c>
       <c r="P8">
-        <v>16.70274081266666</v>
+        <v>16.64358650366667</v>
       </c>
       <c r="Q8">
-        <v>18.00274081266667</v>
+        <v>17.94358650366667</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1547342343309143</v>
+        <v>0.1556033898225844</v>
       </c>
       <c r="T8">
-        <v>1.305004057604831</v>
+        <v>1.315416316434992</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>48.05980312346213</v>
+        <v>41.19411696296755</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1472814825350035</v>
+        <v>0.1469096447989475</v>
       </c>
       <c r="C9">
-        <v>143.3663890304252</v>
+        <v>142.2630531742033</v>
       </c>
       <c r="D9">
-        <v>138.0433890304252</v>
+        <v>138.5510531742033</v>
       </c>
       <c r="E9">
-        <v>-104.223</v>
+        <v>-102.612</v>
       </c>
       <c r="F9">
-        <v>11.277</v>
+        <v>12.888</v>
       </c>
       <c r="G9">
         <v>16.6</v>
@@ -2025,28 +2025,28 @@
         <v>23.36666666666667</v>
       </c>
       <c r="M9">
-        <v>0.5672331000000002</v>
+        <v>0.6482664</v>
       </c>
       <c r="N9">
-        <v>22.79943356666667</v>
+        <v>22.71840026666667</v>
       </c>
       <c r="O9">
-        <v>6.155847063</v>
+        <v>6.133968072</v>
       </c>
       <c r="P9">
-        <v>16.64358650366667</v>
+        <v>16.58443219466667</v>
       </c>
       <c r="Q9">
-        <v>17.94358650366667</v>
+        <v>17.88443219466667</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1556033898225844</v>
+        <v>0.156491439998856</v>
       </c>
       <c r="T9">
-        <v>1.315416316434992</v>
+        <v>1.326054928717984</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>41.19411696296753</v>
+        <v>36.0448523425966</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1469096447989475</v>
+        <v>0.1465378070628915</v>
       </c>
       <c r="C10">
-        <v>142.2630531742033</v>
+        <v>141.1634650407362</v>
       </c>
       <c r="D10">
-        <v>138.5510531742033</v>
+        <v>139.0624650407362</v>
       </c>
       <c r="E10">
-        <v>-102.612</v>
+        <v>-101.001</v>
       </c>
       <c r="F10">
-        <v>12.888</v>
+        <v>14.499</v>
       </c>
       <c r="G10">
         <v>16.6</v>
@@ -2107,28 +2107,28 @@
         <v>23.36666666666667</v>
       </c>
       <c r="M10">
-        <v>0.6482664</v>
+        <v>0.7292997000000001</v>
       </c>
       <c r="N10">
-        <v>22.71840026666667</v>
+        <v>22.63736696666667</v>
       </c>
       <c r="O10">
-        <v>6.133968072</v>
+        <v>6.112089081000001</v>
       </c>
       <c r="P10">
-        <v>16.58443219466667</v>
+        <v>16.52527788566667</v>
       </c>
       <c r="Q10">
-        <v>17.88443219466667</v>
+        <v>17.82527788566667</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.156491439998856</v>
+        <v>0.1573990077614193</v>
       </c>
       <c r="T10">
-        <v>1.326054928717984</v>
+        <v>1.336927356655546</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>36.0448523425966</v>
+        <v>32.03986874897475</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1465378070628915</v>
+        <v>0.1461659693268356</v>
       </c>
       <c r="C11">
-        <v>141.1634650407362</v>
+        <v>140.0676662839257</v>
       </c>
       <c r="D11">
-        <v>139.0624650407362</v>
+        <v>139.5776662839257</v>
       </c>
       <c r="E11">
-        <v>-101.001</v>
+        <v>-99.39000000000001</v>
       </c>
       <c r="F11">
-        <v>14.499</v>
+        <v>16.11</v>
       </c>
       <c r="G11">
         <v>16.6</v>
@@ -2189,28 +2189,28 @@
         <v>23.36666666666667</v>
       </c>
       <c r="M11">
-        <v>0.7292997000000001</v>
+        <v>0.810333</v>
       </c>
       <c r="N11">
-        <v>22.63736696666667</v>
+        <v>22.55633366666667</v>
       </c>
       <c r="O11">
-        <v>6.112089081000001</v>
+        <v>6.09021009</v>
       </c>
       <c r="P11">
-        <v>16.52527788566667</v>
+        <v>16.46612357666667</v>
       </c>
       <c r="Q11">
-        <v>17.82527788566667</v>
+        <v>17.76612357666667</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1573990077614193</v>
+        <v>0.158326743696484</v>
       </c>
       <c r="T11">
-        <v>1.336927356655546</v>
+        <v>1.348041394102833</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>32.03986874897475</v>
+        <v>28.83588187407728</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1461659693268356</v>
+        <v>0.1457941315907796</v>
       </c>
       <c r="C12">
-        <v>140.0676662839257</v>
+        <v>138.9756991772498</v>
       </c>
       <c r="D12">
-        <v>139.5776662839257</v>
+        <v>140.0966991772498</v>
       </c>
       <c r="E12">
-        <v>-99.39000000000001</v>
+        <v>-97.77900000000001</v>
       </c>
       <c r="F12">
-        <v>16.11</v>
+        <v>17.721</v>
       </c>
       <c r="G12">
         <v>16.6</v>
@@ -2271,28 +2271,28 @@
         <v>23.36666666666667</v>
       </c>
       <c r="M12">
-        <v>0.8103330000000001</v>
+        <v>0.8913663000000002</v>
       </c>
       <c r="N12">
-        <v>22.55633366666667</v>
+        <v>22.47530036666667</v>
       </c>
       <c r="O12">
-        <v>6.09021009</v>
+        <v>6.068331099</v>
       </c>
       <c r="P12">
-        <v>16.46612357666667</v>
+        <v>16.40696926766667</v>
       </c>
       <c r="Q12">
-        <v>17.76612357666667</v>
+        <v>17.70696926766667</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.158326743696484</v>
+        <v>0.1592753276300895</v>
       </c>
       <c r="T12">
-        <v>1.348041394102833</v>
+        <v>1.35940518520062</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>28.83588187407728</v>
+        <v>26.21443806734298</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1457941315907796</v>
+        <v>0.1454222938547237</v>
       </c>
       <c r="C13">
-        <v>138.9756991772498</v>
+        <v>137.8876066253251</v>
       </c>
       <c r="D13">
-        <v>140.0966991772498</v>
+        <v>140.6196066253251</v>
       </c>
       <c r="E13">
-        <v>-97.77900000000001</v>
+        <v>-96.16800000000001</v>
       </c>
       <c r="F13">
-        <v>17.721</v>
+        <v>19.332</v>
       </c>
       <c r="G13">
         <v>16.6</v>
@@ -2353,28 +2353,28 @@
         <v>23.36666666666667</v>
       </c>
       <c r="M13">
-        <v>0.8913663000000002</v>
+        <v>0.9723996</v>
       </c>
       <c r="N13">
-        <v>22.47530036666667</v>
+        <v>22.39426706666667</v>
       </c>
       <c r="O13">
-        <v>6.068331099</v>
+        <v>6.046452108</v>
       </c>
       <c r="P13">
-        <v>16.40696926766667</v>
+        <v>16.34781495866667</v>
       </c>
       <c r="Q13">
-        <v>17.70696926766667</v>
+        <v>17.64781495866667</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1592753276300895</v>
+        <v>0.1602454702894587</v>
       </c>
       <c r="T13">
-        <v>1.35940518520062</v>
+        <v>1.371027244277902</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>26.21443806734298</v>
+        <v>24.02990156173107</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1454222938547237</v>
+        <v>0.1450504561186677</v>
       </c>
       <c r="C14">
-        <v>137.8876066253251</v>
+        <v>136.8034321757299</v>
       </c>
       <c r="D14">
-        <v>140.6196066253251</v>
+        <v>141.1464321757299</v>
       </c>
       <c r="E14">
-        <v>-96.16800000000001</v>
+        <v>-94.55700000000002</v>
       </c>
       <c r="F14">
-        <v>19.332</v>
+        <v>20.943</v>
       </c>
       <c r="G14">
         <v>16.6</v>
@@ -2435,28 +2435,28 @@
         <v>23.36666666666667</v>
       </c>
       <c r="M14">
-        <v>0.9723996</v>
+        <v>1.0534329</v>
       </c>
       <c r="N14">
-        <v>22.39426706666667</v>
+        <v>22.31323376666667</v>
       </c>
       <c r="O14">
-        <v>6.046452108</v>
+        <v>6.024573117</v>
       </c>
       <c r="P14">
-        <v>16.34781495866667</v>
+        <v>16.28866064966667</v>
       </c>
       <c r="Q14">
-        <v>17.64781495866667</v>
+        <v>17.58866064966667</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1602454702894587</v>
+        <v>0.1612379150789284</v>
       </c>
       <c r="T14">
-        <v>1.371027244277902</v>
+        <v>1.382916477127076</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>24.02990156173107</v>
+        <v>22.18144759544406</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1450504561186677</v>
+        <v>0.1446786183826117</v>
       </c>
       <c r="C15">
-        <v>136.8034321757299</v>
+        <v>135.7232200310933</v>
       </c>
       <c r="D15">
-        <v>141.1464321757299</v>
+        <v>141.6772200310933</v>
       </c>
       <c r="E15">
-        <v>-94.55700000000002</v>
+        <v>-92.94600000000001</v>
       </c>
       <c r="F15">
-        <v>20.943</v>
+        <v>22.55400000000001</v>
       </c>
       <c r="G15">
         <v>16.6</v>
@@ -2517,28 +2517,28 @@
         <v>23.36666666666667</v>
       </c>
       <c r="M15">
-        <v>1.0534329</v>
+        <v>1.1344662</v>
       </c>
       <c r="N15">
-        <v>22.31323376666667</v>
+        <v>22.23220046666667</v>
       </c>
       <c r="O15">
-        <v>6.024573117</v>
+        <v>6.002694126000001</v>
       </c>
       <c r="P15">
-        <v>16.28866064966667</v>
+        <v>16.22950634066667</v>
       </c>
       <c r="Q15">
-        <v>17.58866064966667</v>
+        <v>17.52950634066667</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1612379150789284</v>
+        <v>0.1622534399797811</v>
       </c>
       <c r="T15">
-        <v>1.382916477127076</v>
+        <v>1.395082203763439</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>22.18144759544406</v>
+        <v>20.59705848148377</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1446786183826117</v>
+        <v>0.1443067806465557</v>
       </c>
       <c r="C16">
-        <v>135.7232200310933</v>
+        <v>134.6470150614586</v>
       </c>
       <c r="D16">
-        <v>141.6772200310933</v>
+        <v>142.2120150614586</v>
       </c>
       <c r="E16">
-        <v>-92.94600000000001</v>
+        <v>-91.33500000000001</v>
       </c>
       <c r="F16">
-        <v>22.55400000000001</v>
+        <v>24.16500000000001</v>
       </c>
       <c r="G16">
         <v>16.6</v>
@@ -2599,28 +2599,28 @@
         <v>23.36666666666667</v>
       </c>
       <c r="M16">
-        <v>1.1344662</v>
+        <v>1.2154995</v>
       </c>
       <c r="N16">
-        <v>22.23220046666667</v>
+        <v>22.15116716666667</v>
       </c>
       <c r="O16">
-        <v>6.002694126000001</v>
+        <v>5.980815135</v>
       </c>
       <c r="P16">
-        <v>16.22950634066667</v>
+        <v>16.17035203166667</v>
       </c>
       <c r="Q16">
-        <v>17.52950634066667</v>
+        <v>17.47035203166667</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1622534399797811</v>
+        <v>0.1632928595841832</v>
       </c>
       <c r="T16">
-        <v>1.395082203763439</v>
+        <v>1.407534182791247</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>20.59705848148377</v>
+        <v>19.22392124938485</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1443067806465557</v>
+        <v>0.1439349429104998</v>
       </c>
       <c r="C17">
-        <v>134.6470150614586</v>
+        <v>133.5748628169277</v>
       </c>
       <c r="D17">
-        <v>142.2120150614586</v>
+        <v>142.7508628169277</v>
       </c>
       <c r="E17">
-        <v>-91.33500000000001</v>
+        <v>-89.72400000000002</v>
       </c>
       <c r="F17">
-        <v>24.165</v>
+        <v>25.776</v>
       </c>
       <c r="G17">
         <v>16.6</v>
@@ -2681,28 +2681,28 @@
         <v>23.36666666666667</v>
       </c>
       <c r="M17">
-        <v>1.2154995</v>
+        <v>1.2965328</v>
       </c>
       <c r="N17">
-        <v>22.15116716666667</v>
+        <v>22.07013386666667</v>
       </c>
       <c r="O17">
-        <v>5.980815135</v>
+        <v>5.958936144</v>
       </c>
       <c r="P17">
-        <v>16.17035203166667</v>
+        <v>16.11119772266667</v>
       </c>
       <c r="Q17">
-        <v>17.47035203166667</v>
+        <v>17.41119772266667</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1632928595841832</v>
+        <v>0.1643570272744045</v>
       </c>
       <c r="T17">
-        <v>1.407534182791247</v>
+        <v>1.420282637510193</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>19.22392124938485</v>
+        <v>18.0224261712983</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1439349429104998</v>
+        <v>0.1435631051744438</v>
       </c>
       <c r="C18">
-        <v>133.5748628169277</v>
+        <v>132.5068095405937</v>
       </c>
       <c r="D18">
-        <v>142.7508628169277</v>
+        <v>143.2938095405937</v>
       </c>
       <c r="E18">
-        <v>-89.72400000000002</v>
+        <v>-88.113</v>
       </c>
       <c r="F18">
-        <v>25.776</v>
+        <v>27.38700000000001</v>
       </c>
       <c r="G18">
         <v>16.6</v>
@@ -2763,28 +2763,28 @@
         <v>23.36666666666667</v>
       </c>
       <c r="M18">
-        <v>1.2965328</v>
+        <v>1.3775661</v>
       </c>
       <c r="N18">
-        <v>22.07013386666667</v>
+        <v>21.98910056666667</v>
       </c>
       <c r="O18">
-        <v>5.958936144</v>
+        <v>5.937057153</v>
       </c>
       <c r="P18">
-        <v>16.11119772266667</v>
+        <v>16.05204341366667</v>
       </c>
       <c r="Q18">
-        <v>17.41119772266667</v>
+        <v>17.35204341366667</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1643570272744045</v>
+        <v>0.1654468375595709</v>
       </c>
       <c r="T18">
-        <v>1.420282637510193</v>
+        <v>1.433338283909114</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>18.0224261712983</v>
+        <v>16.96228345533957</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1435631051744438</v>
+        <v>0.1431912674383878</v>
       </c>
       <c r="C19">
-        <v>132.5068095405937</v>
+        <v>131.4429021817704</v>
       </c>
       <c r="D19">
-        <v>143.2938095405937</v>
+        <v>143.8409021817704</v>
       </c>
       <c r="E19">
-        <v>-88.113</v>
+        <v>-86.50200000000001</v>
       </c>
       <c r="F19">
-        <v>27.38700000000001</v>
+        <v>28.99800000000001</v>
       </c>
       <c r="G19">
         <v>16.6</v>
@@ -2845,28 +2845,28 @@
         <v>23.36666666666667</v>
       </c>
       <c r="M19">
-        <v>1.3775661</v>
+        <v>1.4585994</v>
       </c>
       <c r="N19">
-        <v>21.98910056666667</v>
+        <v>21.90806726666667</v>
       </c>
       <c r="O19">
-        <v>5.937057153</v>
+        <v>5.915178162</v>
       </c>
       <c r="P19">
-        <v>16.05204341366667</v>
+        <v>15.99288910466667</v>
       </c>
       <c r="Q19">
-        <v>17.35204341366667</v>
+        <v>17.29288910466667</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1654468375595709</v>
+        <v>0.1665632285833998</v>
       </c>
       <c r="T19">
-        <v>1.433338283909114</v>
+        <v>1.446712360708008</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>16.96228345533957</v>
+        <v>16.01993437448738</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1431912674383879</v>
+        <v>0.1428194297023319</v>
       </c>
       <c r="C20">
-        <v>131.4429021817704</v>
+        <v>130.3831884095251</v>
       </c>
       <c r="D20">
-        <v>143.8409021817704</v>
+        <v>144.3921884095251</v>
       </c>
       <c r="E20">
-        <v>-86.50200000000001</v>
+        <v>-84.89100000000001</v>
       </c>
       <c r="F20">
-        <v>28.998</v>
+        <v>30.60900000000001</v>
       </c>
       <c r="G20">
         <v>16.6</v>
@@ -2927,28 +2927,28 @@
         <v>23.36666666666667</v>
       </c>
       <c r="M20">
-        <v>1.4585994</v>
+        <v>1.5396327</v>
       </c>
       <c r="N20">
-        <v>21.90806726666667</v>
+        <v>21.82703396666667</v>
       </c>
       <c r="O20">
-        <v>5.915178162</v>
+        <v>5.893299171000001</v>
       </c>
       <c r="P20">
-        <v>15.99288910466667</v>
+        <v>15.93373479566667</v>
       </c>
       <c r="Q20">
-        <v>17.29288910466667</v>
+        <v>17.23373479566667</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1665632285833998</v>
+        <v>0.1677071848176937</v>
       </c>
       <c r="T20">
-        <v>1.446712360708008</v>
+        <v>1.460416661625394</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>16.01993437448738</v>
+        <v>15.17677993372488</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1428194297023319</v>
+        <v>0.1424475919662759</v>
       </c>
       <c r="C21">
-        <v>130.3831884095251</v>
+        <v>129.3277166265251</v>
       </c>
       <c r="D21">
-        <v>144.3921884095251</v>
+        <v>144.9477166265251</v>
       </c>
       <c r="E21">
-        <v>-84.89100000000001</v>
+        <v>-83.28</v>
       </c>
       <c r="F21">
-        <v>30.60900000000001</v>
+        <v>32.22000000000001</v>
       </c>
       <c r="G21">
         <v>16.6</v>
@@ -3009,28 +3009,28 @@
         <v>23.36666666666667</v>
       </c>
       <c r="M21">
-        <v>1.5396327</v>
+        <v>1.620666</v>
       </c>
       <c r="N21">
-        <v>21.82703396666667</v>
+        <v>21.74600066666667</v>
       </c>
       <c r="O21">
-        <v>5.893299171000001</v>
+        <v>5.87142018</v>
       </c>
       <c r="P21">
-        <v>15.93373479566667</v>
+        <v>15.87458048666667</v>
       </c>
       <c r="Q21">
-        <v>17.23373479566667</v>
+        <v>17.17458048666667</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1677071848176937</v>
+        <v>0.1688797399578449</v>
       </c>
       <c r="T21">
-        <v>1.460416661625394</v>
+        <v>1.474463570065714</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>15.17677993372488</v>
+        <v>14.41794093703864</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1424475919662759</v>
+        <v>0.14207575423022</v>
       </c>
       <c r="C22">
-        <v>129.3277166265251</v>
+        <v>128.2765359832035</v>
       </c>
       <c r="D22">
-        <v>144.9477166265251</v>
+        <v>145.5075359832035</v>
       </c>
       <c r="E22">
-        <v>-83.28</v>
+        <v>-81.66900000000001</v>
       </c>
       <c r="F22">
-        <v>32.22000000000001</v>
+        <v>33.83100000000001</v>
       </c>
       <c r="G22">
         <v>16.6</v>
@@ -3091,28 +3091,28 @@
         <v>23.36666666666667</v>
       </c>
       <c r="M22">
-        <v>1.620666</v>
+        <v>1.7016993</v>
       </c>
       <c r="N22">
-        <v>21.74600066666667</v>
+        <v>21.66496736666667</v>
       </c>
       <c r="O22">
-        <v>5.87142018</v>
+        <v>5.849541189</v>
       </c>
       <c r="P22">
-        <v>15.87458048666667</v>
+        <v>15.81542617766667</v>
       </c>
       <c r="Q22">
-        <v>17.17458048666667</v>
+        <v>17.11542617766667</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1688797399578449</v>
+        <v>0.1700819800382531</v>
       </c>
       <c r="T22">
-        <v>1.474463570065714</v>
+        <v>1.488866096441232</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>14.41794093703864</v>
+        <v>13.73137232098918</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.14207575423022</v>
+        <v>0.141703916494164</v>
       </c>
       <c r="C23">
-        <v>128.2765359832035</v>
+        <v>127.2296963922559</v>
       </c>
       <c r="D23">
-        <v>145.5075359832035</v>
+        <v>146.0716963922559</v>
       </c>
       <c r="E23">
-        <v>-81.66900000000001</v>
+        <v>-80.05800000000001</v>
       </c>
       <c r="F23">
-        <v>33.831</v>
+        <v>35.44200000000001</v>
       </c>
       <c r="G23">
         <v>16.6</v>
@@ -3173,28 +3173,28 @@
         <v>23.36666666666667</v>
       </c>
       <c r="M23">
-        <v>1.7016993</v>
+        <v>1.7827326</v>
       </c>
       <c r="N23">
-        <v>21.66496736666667</v>
+        <v>21.58393406666667</v>
       </c>
       <c r="O23">
-        <v>5.849541189</v>
+        <v>5.827662198000001</v>
       </c>
       <c r="P23">
-        <v>15.81542617766667</v>
+        <v>15.75627186866667</v>
       </c>
       <c r="Q23">
-        <v>17.11542617766667</v>
+        <v>17.05627186866667</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1700819800382531</v>
+        <v>0.1713150467873897</v>
       </c>
       <c r="T23">
-        <v>1.488866096441232</v>
+        <v>1.50363791836484</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>13.73137232098918</v>
+        <v>13.10721903367149</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.141703916494164</v>
+        <v>0.141583928758108</v>
       </c>
       <c r="C24">
-        <v>127.2296963922559</v>
+        <v>125.8016791992801</v>
       </c>
       <c r="D24">
-        <v>146.0716963922559</v>
+        <v>146.2546791992801</v>
       </c>
       <c r="E24">
-        <v>-80.05800000000001</v>
+        <v>-78.447</v>
       </c>
       <c r="F24">
-        <v>35.44200000000001</v>
+        <v>37.053</v>
       </c>
       <c r="G24">
         <v>16.6</v>
@@ -3255,45 +3255,45 @@
         <v>23.36666666666667</v>
       </c>
       <c r="M24">
-        <v>1.7827326</v>
+        <v>1.9193454</v>
       </c>
       <c r="N24">
-        <v>21.58393406666667</v>
+        <v>21.44732126666667</v>
       </c>
       <c r="O24">
-        <v>5.827662198000001</v>
+        <v>5.790776742</v>
       </c>
       <c r="P24">
-        <v>15.75627186866667</v>
+        <v>15.65654452466667</v>
       </c>
       <c r="Q24">
-        <v>17.05627186866667</v>
+        <v>16.95654452466667</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1713150467873897</v>
+        <v>0.1725801412442961</v>
       </c>
       <c r="T24">
-        <v>1.50363791836484</v>
+        <v>1.518793423974776</v>
       </c>
       <c r="U24">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V24">
         <v>0.27</v>
       </c>
       <c r="W24">
-        <v>0.03671899999999999</v>
+        <v>0.037814</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y24">
-        <v>13.10721903367149</v>
+        <v>12.174289560736</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.141583928758108</v>
+        <v>0.141223041022052</v>
       </c>
       <c r="C25">
-        <v>125.8016791992801</v>
+        <v>124.7438110162761</v>
       </c>
       <c r="D25">
-        <v>146.2546791992801</v>
+        <v>146.8078110162762</v>
       </c>
       <c r="E25">
-        <v>-78.447</v>
+        <v>-76.83600000000001</v>
       </c>
       <c r="F25">
-        <v>37.053</v>
+        <v>38.66400000000001</v>
       </c>
       <c r="G25">
         <v>16.6</v>
@@ -3337,28 +3337,28 @@
         <v>23.36666666666667</v>
       </c>
       <c r="M25">
-        <v>1.9193454</v>
+        <v>2.0027952</v>
       </c>
       <c r="N25">
-        <v>21.44732126666667</v>
+        <v>21.36387146666667</v>
       </c>
       <c r="O25">
-        <v>5.790776742</v>
+        <v>5.768245296</v>
       </c>
       <c r="P25">
-        <v>15.65654452466667</v>
+        <v>15.59562617066667</v>
       </c>
       <c r="Q25">
-        <v>16.95654452466667</v>
+        <v>16.89562617066667</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1725801412442961</v>
+        <v>0.1738785276605948</v>
       </c>
       <c r="T25">
-        <v>1.518793423974776</v>
+        <v>1.53434775867971</v>
       </c>
       <c r="U25">
         <v>0.0518</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>12.174289560736</v>
+        <v>11.66702749570533</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.141223041022052</v>
+        <v>0.1408621532859961</v>
       </c>
       <c r="C26">
-        <v>124.7438110162762</v>
+        <v>123.6901425801174</v>
       </c>
       <c r="D26">
-        <v>146.8078110162762</v>
+        <v>147.3651425801174</v>
       </c>
       <c r="E26">
-        <v>-76.83600000000001</v>
+        <v>-75.22500000000001</v>
       </c>
       <c r="F26">
-        <v>38.664</v>
+        <v>40.27500000000001</v>
       </c>
       <c r="G26">
         <v>16.6</v>
@@ -3419,28 +3419,28 @@
         <v>23.36666666666667</v>
       </c>
       <c r="M26">
-        <v>2.0027952</v>
+        <v>2.086245</v>
       </c>
       <c r="N26">
-        <v>21.36387146666667</v>
+        <v>21.28042166666667</v>
       </c>
       <c r="O26">
-        <v>5.768245296</v>
+        <v>5.74571385</v>
       </c>
       <c r="P26">
-        <v>15.59562617066667</v>
+        <v>15.53470781666666</v>
       </c>
       <c r="Q26">
-        <v>16.89562617066667</v>
+        <v>16.83470781666666</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1738785276605948</v>
+        <v>0.1752115377146614</v>
       </c>
       <c r="T26">
-        <v>1.53434775867971</v>
+        <v>1.550316875643443</v>
       </c>
       <c r="U26">
         <v>0.0518</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>11.66702749570534</v>
+        <v>11.20034639587712</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1408621532859961</v>
+        <v>0.1405012655499401</v>
       </c>
       <c r="C27">
-        <v>123.6901425801174</v>
+        <v>122.6407219040099</v>
       </c>
       <c r="D27">
-        <v>147.3651425801174</v>
+        <v>147.9267219040099</v>
       </c>
       <c r="E27">
-        <v>-75.22500000000001</v>
+        <v>-73.614</v>
       </c>
       <c r="F27">
-        <v>40.27500000000001</v>
+        <v>41.88600000000001</v>
       </c>
       <c r="G27">
         <v>16.6</v>
@@ -3501,28 +3501,28 @@
         <v>23.36666666666667</v>
       </c>
       <c r="M27">
-        <v>2.086245</v>
+        <v>2.1696948</v>
       </c>
       <c r="N27">
-        <v>21.28042166666667</v>
+        <v>21.19697186666667</v>
       </c>
       <c r="O27">
-        <v>5.74571385</v>
+        <v>5.723182404</v>
       </c>
       <c r="P27">
-        <v>15.53470781666666</v>
+        <v>15.47378946266667</v>
       </c>
       <c r="Q27">
-        <v>16.83470781666666</v>
+        <v>16.77378946266667</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1752115377146614</v>
+        <v>0.1765805750674866</v>
       </c>
       <c r="T27">
-        <v>1.550316875643443</v>
+        <v>1.566717590362951</v>
       </c>
       <c r="U27">
         <v>0.0518</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>11.20034639587712</v>
+        <v>10.76956384218954</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1405012655499401</v>
+        <v>0.1401403778138842</v>
       </c>
       <c r="C28">
-        <v>122.6407219040099</v>
+        <v>121.5955977358349</v>
       </c>
       <c r="D28">
-        <v>147.9267219040099</v>
+        <v>148.4925977358349</v>
       </c>
       <c r="E28">
-        <v>-73.614</v>
+        <v>-72.00300000000001</v>
       </c>
       <c r="F28">
-        <v>41.88600000000001</v>
+        <v>43.49700000000001</v>
       </c>
       <c r="G28">
         <v>16.6</v>
@@ -3583,28 +3583,28 @@
         <v>23.36666666666667</v>
       </c>
       <c r="M28">
-        <v>2.1696948</v>
+        <v>2.2531446</v>
       </c>
       <c r="N28">
-        <v>21.19697186666667</v>
+        <v>21.11352206666667</v>
       </c>
       <c r="O28">
-        <v>5.723182404</v>
+        <v>5.700650958000001</v>
       </c>
       <c r="P28">
-        <v>15.47378946266667</v>
+        <v>15.41287110866667</v>
       </c>
       <c r="Q28">
-        <v>16.77378946266667</v>
+        <v>16.71287110866667</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1765805750674866</v>
+        <v>0.177987120292992</v>
       </c>
       <c r="T28">
-        <v>1.566717590362951</v>
+        <v>1.58356763973231</v>
       </c>
       <c r="U28">
         <v>0.0518</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>10.76956384218954</v>
+        <v>10.37069110729363</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1401403778138842</v>
+        <v>0.1397794900778282</v>
       </c>
       <c r="C29">
-        <v>121.5955977358349</v>
+        <v>120.5548195722545</v>
       </c>
       <c r="D29">
-        <v>148.4925977358349</v>
+        <v>149.0628195722545</v>
       </c>
       <c r="E29">
-        <v>-72.00300000000001</v>
+        <v>-70.392</v>
       </c>
       <c r="F29">
-        <v>43.49700000000001</v>
+        <v>45.10800000000001</v>
       </c>
       <c r="G29">
         <v>16.6</v>
@@ -3665,28 +3665,28 @@
         <v>23.36666666666667</v>
       </c>
       <c r="M29">
-        <v>2.2531446</v>
+        <v>2.336594400000001</v>
       </c>
       <c r="N29">
-        <v>21.11352206666667</v>
+        <v>21.03007226666667</v>
       </c>
       <c r="O29">
-        <v>5.700650958000001</v>
+        <v>5.678119512</v>
       </c>
       <c r="P29">
-        <v>15.41287110866667</v>
+        <v>15.35195275466667</v>
       </c>
       <c r="Q29">
-        <v>16.71287110866667</v>
+        <v>16.65195275466667</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.177987120292992</v>
+        <v>0.1794327362192058</v>
       </c>
       <c r="T29">
-        <v>1.58356763973231</v>
+        <v>1.600885746028595</v>
       </c>
       <c r="U29">
         <v>0.0518</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>10.37069110729363</v>
+        <v>10.00030928203314</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1397794900778282</v>
+        <v>0.1397784923417722</v>
       </c>
       <c r="C30">
-        <v>120.5548195722545</v>
+        <v>118.9454021189201</v>
       </c>
       <c r="D30">
-        <v>149.0628195722545</v>
+        <v>149.0644021189201</v>
       </c>
       <c r="E30">
-        <v>-70.392</v>
+        <v>-68.78100000000001</v>
       </c>
       <c r="F30">
-        <v>45.10800000000001</v>
+        <v>46.71900000000002</v>
       </c>
       <c r="G30">
         <v>16.6</v>
@@ -3747,45 +3747,45 @@
         <v>23.36666666666667</v>
       </c>
       <c r="M30">
-        <v>2.336594400000001</v>
+        <v>2.499466500000001</v>
       </c>
       <c r="N30">
-        <v>21.03007226666667</v>
+        <v>20.86720016666667</v>
       </c>
       <c r="O30">
-        <v>5.678119512</v>
+        <v>5.634144045</v>
       </c>
       <c r="P30">
-        <v>15.35195275466667</v>
+        <v>15.23305612166667</v>
       </c>
       <c r="Q30">
-        <v>16.65195275466667</v>
+        <v>16.53305612166667</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1794327362192058</v>
+        <v>0.1809190737208059</v>
       </c>
       <c r="T30">
-        <v>1.600885746028595</v>
+        <v>1.618691686305057</v>
       </c>
       <c r="U30">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V30">
         <v>0.27</v>
       </c>
       <c r="W30">
-        <v>0.037814</v>
+        <v>0.039055</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y30">
-        <v>10.00030928203314</v>
+        <v>9.348661671067269</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1397784923417722</v>
+        <v>0.1394300146057162</v>
       </c>
       <c r="C31">
-        <v>118.9454021189201</v>
+        <v>117.8891988429801</v>
       </c>
       <c r="D31">
-        <v>149.0644021189201</v>
+        <v>149.6191988429801</v>
       </c>
       <c r="E31">
-        <v>-68.78100000000001</v>
+        <v>-67.17000000000002</v>
       </c>
       <c r="F31">
-        <v>46.719</v>
+        <v>48.33000000000001</v>
       </c>
       <c r="G31">
         <v>16.6</v>
@@ -3829,28 +3829,28 @@
         <v>23.36666666666667</v>
       </c>
       <c r="M31">
-        <v>2.4994665</v>
+        <v>2.585655</v>
       </c>
       <c r="N31">
-        <v>20.86720016666667</v>
+        <v>20.78101166666667</v>
       </c>
       <c r="O31">
-        <v>5.634144045</v>
+        <v>5.610873150000001</v>
       </c>
       <c r="P31">
-        <v>15.23305612166667</v>
+        <v>15.17013851666667</v>
       </c>
       <c r="Q31">
-        <v>16.53305612166667</v>
+        <v>16.47013851666667</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1809190737208059</v>
+        <v>0.1824478780081661</v>
       </c>
       <c r="T31">
-        <v>1.618691686305057</v>
+        <v>1.637006367732275</v>
       </c>
       <c r="U31">
         <v>0.0535</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>9.348661671067273</v>
+        <v>9.03703961536503</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1394300146057162</v>
+        <v>0.1390815368696603</v>
       </c>
       <c r="C32">
-        <v>117.8891988429801</v>
+        <v>116.8371407454506</v>
       </c>
       <c r="D32">
-        <v>149.6191988429801</v>
+        <v>150.1781407454506</v>
       </c>
       <c r="E32">
-        <v>-67.17000000000002</v>
+        <v>-65.559</v>
       </c>
       <c r="F32">
-        <v>48.33000000000001</v>
+        <v>49.94100000000001</v>
       </c>
       <c r="G32">
         <v>16.6</v>
@@ -3911,28 +3911,28 @@
         <v>23.36666666666667</v>
       </c>
       <c r="M32">
-        <v>2.585655</v>
+        <v>2.6718435</v>
       </c>
       <c r="N32">
-        <v>20.78101166666667</v>
+        <v>20.69482316666667</v>
       </c>
       <c r="O32">
-        <v>5.610873150000001</v>
+        <v>5.587602255</v>
       </c>
       <c r="P32">
-        <v>15.17013851666667</v>
+        <v>15.10722091166667</v>
       </c>
       <c r="Q32">
-        <v>16.47013851666667</v>
+        <v>16.40722091166667</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1824478780081661</v>
+        <v>0.1840209954632758</v>
       </c>
       <c r="T32">
-        <v>1.637006367732275</v>
+        <v>1.655851909490717</v>
       </c>
       <c r="U32">
         <v>0.0535</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>9.03703961536503</v>
+        <v>8.74552220841777</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1390815368696603</v>
+        <v>0.1387330591336043</v>
       </c>
       <c r="C33">
-        <v>116.8371407454506</v>
+        <v>115.7892744567475</v>
       </c>
       <c r="D33">
-        <v>150.1781407454506</v>
+        <v>150.7412744567475</v>
       </c>
       <c r="E33">
-        <v>-65.559</v>
+        <v>-63.94800000000001</v>
       </c>
       <c r="F33">
-        <v>49.94100000000001</v>
+        <v>51.55200000000001</v>
       </c>
       <c r="G33">
         <v>16.6</v>
@@ -3993,28 +3993,28 @@
         <v>23.36666666666667</v>
       </c>
       <c r="M33">
-        <v>2.6718435</v>
+        <v>2.758032</v>
       </c>
       <c r="N33">
-        <v>20.69482316666667</v>
+        <v>20.60863466666667</v>
       </c>
       <c r="O33">
-        <v>5.587602255</v>
+        <v>5.564331360000001</v>
       </c>
       <c r="P33">
-        <v>15.10722091166667</v>
+        <v>15.04430330666667</v>
       </c>
       <c r="Q33">
-        <v>16.40722091166667</v>
+        <v>16.34430330666667</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1840209954632758</v>
+        <v>0.1856403810788299</v>
       </c>
       <c r="T33">
-        <v>1.655851909490717</v>
+        <v>1.675251731889113</v>
       </c>
       <c r="U33">
         <v>0.0535</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>8.74552220841777</v>
+        <v>8.472224639404715</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1387330591336043</v>
+        <v>0.1383845813975483</v>
       </c>
       <c r="C34">
-        <v>115.7892744567475</v>
+        <v>114.745647309332</v>
       </c>
       <c r="D34">
-        <v>150.7412744567475</v>
+        <v>151.3086473093321</v>
       </c>
       <c r="E34">
-        <v>-63.94800000000001</v>
+        <v>-62.337</v>
       </c>
       <c r="F34">
-        <v>51.55200000000001</v>
+        <v>53.16300000000001</v>
       </c>
       <c r="G34">
         <v>16.6</v>
@@ -4075,28 +4075,28 @@
         <v>23.36666666666667</v>
       </c>
       <c r="M34">
-        <v>2.758032</v>
+        <v>2.8442205</v>
       </c>
       <c r="N34">
-        <v>20.60863466666667</v>
+        <v>20.52244616666667</v>
       </c>
       <c r="O34">
-        <v>5.564331360000001</v>
+        <v>5.541060465000001</v>
       </c>
       <c r="P34">
-        <v>15.04430330666667</v>
+        <v>14.98138570166667</v>
       </c>
       <c r="Q34">
-        <v>16.34430330666667</v>
+        <v>16.28138570166667</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1856403810788299</v>
+        <v>0.187308106563505</v>
       </c>
       <c r="T34">
-        <v>1.675251731889113</v>
+        <v>1.695230653463581</v>
       </c>
       <c r="U34">
         <v>0.0535</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>8.472224639404715</v>
+        <v>8.215490559422754</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1383845813975483</v>
+        <v>0.1380361036614924</v>
       </c>
       <c r="C35">
-        <v>114.745647309332</v>
+        <v>113.7063073509743</v>
       </c>
       <c r="D35">
-        <v>151.3086473093321</v>
+        <v>151.8803073509743</v>
       </c>
       <c r="E35">
-        <v>-62.337</v>
+        <v>-60.726</v>
       </c>
       <c r="F35">
-        <v>53.16300000000001</v>
+        <v>54.77400000000002</v>
       </c>
       <c r="G35">
         <v>16.6</v>
@@ -4157,28 +4157,28 @@
         <v>23.36666666666667</v>
       </c>
       <c r="M35">
-        <v>2.8442205</v>
+        <v>2.930409000000001</v>
       </c>
       <c r="N35">
-        <v>20.52244616666667</v>
+        <v>20.43625766666667</v>
       </c>
       <c r="O35">
-        <v>5.541060465000001</v>
+        <v>5.517789570000001</v>
       </c>
       <c r="P35">
-        <v>14.98138570166667</v>
+        <v>14.91846809666666</v>
       </c>
       <c r="Q35">
-        <v>16.28138570166667</v>
+        <v>16.21846809666667</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.187308106563505</v>
+        <v>0.1890263691840794</v>
       </c>
       <c r="T35">
-        <v>1.695230653463581</v>
+        <v>1.715814996903942</v>
       </c>
       <c r="U35">
         <v>0.0535</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>8.215490559422754</v>
+        <v>7.973858484145612</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1380361036614924</v>
+        <v>0.1376876259254364</v>
       </c>
       <c r="C36">
-        <v>113.7063073509743</v>
+        <v>112.6713033583159</v>
       </c>
       <c r="D36">
-        <v>151.8803073509743</v>
+        <v>152.4563033583159</v>
       </c>
       <c r="E36">
-        <v>-60.726</v>
+        <v>-59.115</v>
       </c>
       <c r="F36">
-        <v>54.77400000000002</v>
+        <v>56.38500000000001</v>
       </c>
       <c r="G36">
         <v>16.6</v>
@@ -4239,28 +4239,28 @@
         <v>23.36666666666667</v>
       </c>
       <c r="M36">
-        <v>2.930409000000001</v>
+        <v>3.0165975</v>
       </c>
       <c r="N36">
-        <v>20.43625766666667</v>
+        <v>20.35006916666667</v>
       </c>
       <c r="O36">
-        <v>5.517789570000001</v>
+        <v>5.494518675000001</v>
       </c>
       <c r="P36">
-        <v>14.91846809666666</v>
+        <v>14.85555049166667</v>
       </c>
       <c r="Q36">
-        <v>16.21846809666667</v>
+        <v>16.15555049166667</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1890263691840794</v>
+        <v>0.1907975014237483</v>
       </c>
       <c r="T36">
-        <v>1.715814996903942</v>
+        <v>1.737032704757852</v>
       </c>
       <c r="U36">
         <v>0.0535</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>7.973858484145612</v>
+        <v>7.746033956027167</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1376876259254364</v>
+        <v>0.1375493881893804</v>
       </c>
       <c r="C37">
-        <v>112.6713033583159</v>
+        <v>111.2900074973802</v>
       </c>
       <c r="D37">
-        <v>152.4563033583159</v>
+        <v>152.6860074973802</v>
       </c>
       <c r="E37">
-        <v>-59.115</v>
+        <v>-57.504</v>
       </c>
       <c r="F37">
-        <v>56.38500000000001</v>
+        <v>57.99600000000002</v>
       </c>
       <c r="G37">
         <v>16.6</v>
@@ -4321,45 +4321,45 @@
         <v>23.36666666666667</v>
       </c>
       <c r="M37">
-        <v>3.0165975</v>
+        <v>3.149182800000001</v>
       </c>
       <c r="N37">
-        <v>20.35006916666667</v>
+        <v>20.21748386666667</v>
       </c>
       <c r="O37">
-        <v>5.494518675000001</v>
+        <v>5.458720644</v>
       </c>
       <c r="P37">
-        <v>14.85555049166667</v>
+        <v>14.75876322266667</v>
       </c>
       <c r="Q37">
-        <v>16.15555049166667</v>
+        <v>16.05876322266667</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1907975014237483</v>
+        <v>0.1926239815459069</v>
       </c>
       <c r="T37">
-        <v>1.737032704757852</v>
+        <v>1.758913465982197</v>
       </c>
       <c r="U37">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V37">
         <v>0.27</v>
       </c>
       <c r="W37">
-        <v>0.039055</v>
+        <v>0.039639</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y37">
-        <v>7.746033956027167</v>
+        <v>7.419914355770856</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1375493881893805</v>
+        <v>0.1372067504533245</v>
       </c>
       <c r="C38">
-        <v>111.2900074973801</v>
+        <v>110.2513502147054</v>
       </c>
       <c r="D38">
-        <v>152.6860074973801</v>
+        <v>153.2583502147054</v>
       </c>
       <c r="E38">
-        <v>-57.504</v>
+        <v>-55.89300000000001</v>
       </c>
       <c r="F38">
-        <v>57.99600000000001</v>
+        <v>59.60700000000001</v>
       </c>
       <c r="G38">
         <v>16.6</v>
@@ -4403,28 +4403,28 @@
         <v>23.36666666666667</v>
       </c>
       <c r="M38">
-        <v>3.149182800000001</v>
+        <v>3.2366601</v>
       </c>
       <c r="N38">
-        <v>20.21748386666667</v>
+        <v>20.13000656666667</v>
       </c>
       <c r="O38">
-        <v>5.458720644</v>
+        <v>5.435101773</v>
       </c>
       <c r="P38">
-        <v>14.75876322266667</v>
+        <v>14.69490479366667</v>
       </c>
       <c r="Q38">
-        <v>16.05876322266667</v>
+        <v>15.99490479366667</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1926239815459069</v>
+        <v>0.1945084451640071</v>
       </c>
       <c r="T38">
-        <v>1.758913465982197</v>
+        <v>1.781488854546997</v>
       </c>
       <c r="U38">
         <v>0.0543</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>7.419914355770857</v>
+        <v>7.219376129939212</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1372067504533245</v>
+        <v>0.1368641127172685</v>
       </c>
       <c r="C39">
-        <v>110.2513502147054</v>
+        <v>109.2169999242598</v>
       </c>
       <c r="D39">
-        <v>153.2583502147054</v>
+        <v>153.8349999242598</v>
       </c>
       <c r="E39">
-        <v>-55.89300000000001</v>
+        <v>-54.282</v>
       </c>
       <c r="F39">
-        <v>59.60700000000001</v>
+        <v>61.21800000000001</v>
       </c>
       <c r="G39">
         <v>16.6</v>
@@ -4485,28 +4485,28 @@
         <v>23.36666666666667</v>
       </c>
       <c r="M39">
-        <v>3.2366601</v>
+        <v>3.324137400000001</v>
       </c>
       <c r="N39">
-        <v>20.13000656666667</v>
+        <v>20.04252926666667</v>
       </c>
       <c r="O39">
-        <v>5.435101773</v>
+        <v>5.411482902</v>
       </c>
       <c r="P39">
-        <v>14.69490479366667</v>
+        <v>14.63104636466667</v>
       </c>
       <c r="Q39">
-        <v>15.99490479366667</v>
+        <v>15.93104636466667</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1945084451640071</v>
+        <v>0.1964536979310782</v>
       </c>
       <c r="T39">
-        <v>1.781488854546997</v>
+        <v>1.804792481452597</v>
       </c>
       <c r="U39">
         <v>0.0543</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>7.219376129939212</v>
+        <v>7.029392547572391</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1368641127172685</v>
+        <v>0.1365214749812125</v>
       </c>
       <c r="C40">
-        <v>109.2169999242598</v>
+        <v>108.1870054261118</v>
       </c>
       <c r="D40">
-        <v>153.8349999242598</v>
+        <v>154.4160054261118</v>
       </c>
       <c r="E40">
-        <v>-54.282</v>
+        <v>-52.67100000000001</v>
       </c>
       <c r="F40">
-        <v>61.21800000000001</v>
+        <v>62.82900000000001</v>
       </c>
       <c r="G40">
         <v>16.6</v>
@@ -4567,28 +4567,28 @@
         <v>23.36666666666667</v>
       </c>
       <c r="M40">
-        <v>3.324137400000001</v>
+        <v>3.4116147</v>
       </c>
       <c r="N40">
-        <v>20.04252926666667</v>
+        <v>19.95505196666667</v>
       </c>
       <c r="O40">
-        <v>5.411482902</v>
+        <v>5.387864031</v>
       </c>
       <c r="P40">
-        <v>14.63104636466667</v>
+        <v>14.56718793566667</v>
       </c>
       <c r="Q40">
-        <v>15.93104636466667</v>
+        <v>15.86718793566667</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1964536979310782</v>
+        <v>0.1984627294773976</v>
       </c>
       <c r="T40">
-        <v>1.804792481452597</v>
+        <v>1.828860161699364</v>
       </c>
       <c r="U40">
         <v>0.0543</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>7.029392547572391</v>
+        <v>6.849151713019253</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1365214749812125</v>
+        <v>0.1361788372451566</v>
       </c>
       <c r="C41">
-        <v>108.1870054261118</v>
+        <v>107.1614162603593</v>
       </c>
       <c r="D41">
-        <v>154.4160054261118</v>
+        <v>155.0014162603593</v>
       </c>
       <c r="E41">
-        <v>-52.67100000000001</v>
+        <v>-51.06</v>
       </c>
       <c r="F41">
-        <v>62.82900000000001</v>
+        <v>64.44000000000001</v>
       </c>
       <c r="G41">
         <v>16.6</v>
@@ -4649,28 +4649,28 @@
         <v>23.36666666666667</v>
       </c>
       <c r="M41">
-        <v>3.4116147</v>
+        <v>3.499092000000001</v>
       </c>
       <c r="N41">
-        <v>19.95505196666667</v>
+        <v>19.86757466666667</v>
       </c>
       <c r="O41">
-        <v>5.387864031</v>
+        <v>5.36424516</v>
       </c>
       <c r="P41">
-        <v>14.56718793566667</v>
+        <v>14.50332950666667</v>
       </c>
       <c r="Q41">
-        <v>15.86718793566667</v>
+        <v>15.80332950666667</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1984627294773976</v>
+        <v>0.2005387287419276</v>
       </c>
       <c r="T41">
-        <v>1.828860161699364</v>
+        <v>1.853730097954358</v>
       </c>
       <c r="U41">
         <v>0.0543</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>6.849151713019253</v>
+        <v>6.677922920193772</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1361788372451566</v>
+        <v>0.1358361995091006</v>
       </c>
       <c r="C42">
-        <v>107.1614162603593</v>
+        <v>106.1402827212105</v>
       </c>
       <c r="D42">
-        <v>155.0014162603593</v>
+        <v>155.5912827212105</v>
       </c>
       <c r="E42">
-        <v>-51.06</v>
+        <v>-49.449</v>
       </c>
       <c r="F42">
-        <v>64.44000000000001</v>
+        <v>66.05100000000002</v>
       </c>
       <c r="G42">
         <v>16.6</v>
@@ -4731,28 +4731,28 @@
         <v>23.36666666666667</v>
       </c>
       <c r="M42">
-        <v>3.499092000000001</v>
+        <v>3.586569300000001</v>
       </c>
       <c r="N42">
-        <v>19.86757466666667</v>
+        <v>19.78009736666667</v>
       </c>
       <c r="O42">
-        <v>5.36424516</v>
+        <v>5.340626289</v>
       </c>
       <c r="P42">
-        <v>14.50332950666667</v>
+        <v>14.43947107766667</v>
       </c>
       <c r="Q42">
-        <v>15.80332950666667</v>
+        <v>15.73947107766667</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.2005387287419276</v>
+        <v>0.2026851008628824</v>
       </c>
       <c r="T42">
-        <v>1.853730097954358</v>
+        <v>1.879443082895961</v>
       </c>
       <c r="U42">
         <v>0.0543</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>6.677922920193772</v>
+        <v>6.515046751408557</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1358361995091006</v>
+        <v>0.1354935617730446</v>
       </c>
       <c r="C43">
-        <v>106.1402827212105</v>
+        <v>105.1236558713875</v>
       </c>
       <c r="D43">
-        <v>155.5912827212105</v>
+        <v>156.1856558713875</v>
       </c>
       <c r="E43">
-        <v>-49.449</v>
+        <v>-47.83799999999999</v>
       </c>
       <c r="F43">
-        <v>66.05100000000002</v>
+        <v>67.66200000000002</v>
       </c>
       <c r="G43">
         <v>16.6</v>
@@ -4813,28 +4813,28 @@
         <v>23.36666666666667</v>
       </c>
       <c r="M43">
-        <v>3.586569300000001</v>
+        <v>3.674046600000001</v>
       </c>
       <c r="N43">
-        <v>19.78009736666667</v>
+        <v>19.69262006666667</v>
       </c>
       <c r="O43">
-        <v>5.340626289</v>
+        <v>5.317007418</v>
       </c>
       <c r="P43">
-        <v>14.43947107766667</v>
+        <v>14.37561264866667</v>
       </c>
       <c r="Q43">
-        <v>15.73947107766667</v>
+        <v>15.67561264866667</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.2026851008628824</v>
+        <v>0.2049054858155942</v>
       </c>
       <c r="T43">
-        <v>1.879443082895961</v>
+        <v>1.906042722490722</v>
       </c>
       <c r="U43">
         <v>0.0543</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>6.515046751408557</v>
+        <v>6.359926590660733</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1354935617730446</v>
+        <v>0.1351509240369887</v>
       </c>
       <c r="C44">
-        <v>105.1236558713875</v>
+        <v>104.1115875568621</v>
       </c>
       <c r="D44">
-        <v>156.1856558713875</v>
+        <v>156.7845875568621</v>
       </c>
       <c r="E44">
-        <v>-47.83800000000001</v>
+        <v>-46.227</v>
       </c>
       <c r="F44">
-        <v>67.66200000000001</v>
+        <v>69.27300000000001</v>
       </c>
       <c r="G44">
         <v>16.6</v>
@@ -4895,28 +4895,28 @@
         <v>23.36666666666667</v>
       </c>
       <c r="M44">
-        <v>3.6740466</v>
+        <v>3.761523900000001</v>
       </c>
       <c r="N44">
-        <v>19.69262006666667</v>
+        <v>19.60514276666667</v>
       </c>
       <c r="O44">
-        <v>5.317007418</v>
+        <v>5.293388547</v>
       </c>
       <c r="P44">
-        <v>14.37561264866667</v>
+        <v>14.31175421966667</v>
       </c>
       <c r="Q44">
-        <v>15.67561264866667</v>
+        <v>15.61175421966667</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.2049054858155942</v>
+        <v>0.2072037790122608</v>
       </c>
       <c r="T44">
-        <v>1.906042722490722</v>
+        <v>1.933575682773019</v>
       </c>
       <c r="U44">
         <v>0.0543</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>6.359926590660734</v>
+        <v>6.212021321110485</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1351509240369887</v>
+        <v>0.1351294863009327</v>
       </c>
       <c r="C45">
-        <v>104.1115875568621</v>
+        <v>102.5382135048538</v>
       </c>
       <c r="D45">
-        <v>156.7845875568621</v>
+        <v>156.8222135048539</v>
       </c>
       <c r="E45">
-        <v>-46.227</v>
+        <v>-44.616</v>
       </c>
       <c r="F45">
-        <v>69.27300000000001</v>
+        <v>70.88400000000001</v>
       </c>
       <c r="G45">
         <v>16.6</v>
@@ -4977,45 +4977,45 @@
         <v>23.36666666666667</v>
       </c>
       <c r="M45">
-        <v>3.761523900000001</v>
+        <v>3.919885200000001</v>
       </c>
       <c r="N45">
-        <v>19.60514276666667</v>
+        <v>19.44678146666667</v>
       </c>
       <c r="O45">
-        <v>5.293388547</v>
+        <v>5.250630996000001</v>
       </c>
       <c r="P45">
-        <v>14.31175421966667</v>
+        <v>14.19615047066667</v>
       </c>
       <c r="Q45">
-        <v>15.61175421966667</v>
+        <v>15.49615047066667</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.2072037790122608</v>
+        <v>0.2095841541088084</v>
       </c>
       <c r="T45">
-        <v>1.933575682773019</v>
+        <v>1.962091963065398</v>
       </c>
       <c r="U45">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V45">
         <v>0.27</v>
       </c>
       <c r="W45">
-        <v>0.039639</v>
+        <v>0.040369</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y45">
-        <v>6.212021321110485</v>
+        <v>5.96105892761009</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1351294863009327</v>
+        <v>0.1347941485648768</v>
       </c>
       <c r="C46">
-        <v>102.5382135048538</v>
+        <v>101.5181333224828</v>
       </c>
       <c r="D46">
-        <v>156.8222135048539</v>
+        <v>157.4131333224828</v>
       </c>
       <c r="E46">
-        <v>-44.616</v>
+        <v>-43.005</v>
       </c>
       <c r="F46">
-        <v>70.88400000000001</v>
+        <v>72.49500000000002</v>
       </c>
       <c r="G46">
         <v>16.6</v>
@@ -5059,28 +5059,28 @@
         <v>23.36666666666667</v>
       </c>
       <c r="M46">
-        <v>3.919885200000001</v>
+        <v>4.008973500000002</v>
       </c>
       <c r="N46">
-        <v>19.44678146666667</v>
+        <v>19.35769316666666</v>
       </c>
       <c r="O46">
-        <v>5.250630996000001</v>
+        <v>5.226577154999999</v>
       </c>
       <c r="P46">
-        <v>14.19615047066667</v>
+        <v>14.13111601166666</v>
       </c>
       <c r="Q46">
-        <v>15.49615047066667</v>
+        <v>15.43111601166667</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.2095841541088084</v>
+        <v>0.2120510882997759</v>
       </c>
       <c r="T46">
-        <v>1.962091963065398</v>
+        <v>1.991645199004773</v>
       </c>
       <c r="U46">
         <v>0.0553</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>5.96105892761009</v>
+        <v>5.828590951440975</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1347941485648768</v>
+        <v>0.1344588108288208</v>
       </c>
       <c r="C47">
-        <v>101.5181333224828</v>
+        <v>100.5025232590313</v>
       </c>
       <c r="D47">
-        <v>157.4131333224828</v>
+        <v>158.0085232590313</v>
       </c>
       <c r="E47">
-        <v>-43.005</v>
+        <v>-41.39400000000001</v>
       </c>
       <c r="F47">
-        <v>72.49500000000002</v>
+        <v>74.10600000000001</v>
       </c>
       <c r="G47">
         <v>16.6</v>
@@ -5141,28 +5141,28 @@
         <v>23.36666666666667</v>
       </c>
       <c r="M47">
-        <v>4.008973500000002</v>
+        <v>4.098061800000001</v>
       </c>
       <c r="N47">
-        <v>19.35769316666666</v>
+        <v>19.26860486666667</v>
       </c>
       <c r="O47">
-        <v>5.226577154999999</v>
+        <v>5.202523314</v>
       </c>
       <c r="P47">
-        <v>14.13111601166666</v>
+        <v>14.06608155266667</v>
       </c>
       <c r="Q47">
-        <v>15.43111601166667</v>
+        <v>15.36608155266667</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.2120510882997759</v>
+        <v>0.2146093904237421</v>
       </c>
       <c r="T47">
-        <v>1.991645199004773</v>
+        <v>2.022292999238199</v>
       </c>
       <c r="U47">
         <v>0.0553</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>5.828590951440975</v>
+        <v>5.701882452496608</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1344588108288208</v>
+        <v>0.1341234730927648</v>
       </c>
       <c r="C48">
-        <v>100.5025232590313</v>
+        <v>99.49143422960168</v>
       </c>
       <c r="D48">
-        <v>158.0085232590313</v>
+        <v>158.6084342296017</v>
       </c>
       <c r="E48">
-        <v>-41.39400000000001</v>
+        <v>-39.783</v>
       </c>
       <c r="F48">
-        <v>74.10600000000001</v>
+        <v>75.71700000000001</v>
       </c>
       <c r="G48">
         <v>16.6</v>
@@ -5223,28 +5223,28 @@
         <v>23.36666666666667</v>
       </c>
       <c r="M48">
-        <v>4.098061800000001</v>
+        <v>4.187150100000001</v>
       </c>
       <c r="N48">
-        <v>19.26860486666667</v>
+        <v>19.17951656666667</v>
       </c>
       <c r="O48">
-        <v>5.202523314</v>
+        <v>5.178469473000001</v>
       </c>
       <c r="P48">
-        <v>14.06608155266667</v>
+        <v>14.00104709366667</v>
       </c>
       <c r="Q48">
-        <v>15.36608155266667</v>
+        <v>15.30104709366667</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.2146093904237421</v>
+        <v>0.2172642322504996</v>
       </c>
       <c r="T48">
-        <v>2.022292999238199</v>
+        <v>2.05409732023515</v>
       </c>
       <c r="U48">
         <v>0.0553</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>5.701882452496608</v>
+        <v>5.580565804571147</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1341234730927648</v>
+        <v>0.1337881353567088</v>
       </c>
       <c r="C49">
-        <v>99.49143422960168</v>
+        <v>98.48491792548084</v>
       </c>
       <c r="D49">
-        <v>158.6084342296017</v>
+        <v>159.2129179254809</v>
       </c>
       <c r="E49">
-        <v>-39.783</v>
+        <v>-38.172</v>
       </c>
       <c r="F49">
-        <v>75.71700000000001</v>
+        <v>77.32800000000002</v>
       </c>
       <c r="G49">
         <v>16.6</v>
@@ -5305,28 +5305,28 @@
         <v>23.36666666666667</v>
       </c>
       <c r="M49">
-        <v>4.187150100000001</v>
+        <v>4.276238400000001</v>
       </c>
       <c r="N49">
-        <v>19.17951656666667</v>
+        <v>19.09042826666667</v>
       </c>
       <c r="O49">
-        <v>5.178469473000001</v>
+        <v>5.154415632</v>
       </c>
       <c r="P49">
-        <v>14.00104709366667</v>
+        <v>13.93601263466667</v>
       </c>
       <c r="Q49">
-        <v>15.30104709366667</v>
+        <v>15.23601263466667</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.2172642322504996</v>
+        <v>0.2200211833782862</v>
       </c>
       <c r="T49">
-        <v>2.05409732023515</v>
+        <v>2.087124884347369</v>
       </c>
       <c r="U49">
         <v>0.0553</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>5.580565804571147</v>
+        <v>5.464304016975915</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1337881353567088</v>
+        <v>0.1334527976206529</v>
       </c>
       <c r="C50">
-        <v>98.48491792548086</v>
+        <v>97.48302682898735</v>
       </c>
       <c r="D50">
-        <v>159.2129179254809</v>
+        <v>159.8220268289874</v>
       </c>
       <c r="E50">
-        <v>-38.17200000000001</v>
+        <v>-36.56100000000001</v>
       </c>
       <c r="F50">
-        <v>77.328</v>
+        <v>78.93900000000001</v>
       </c>
       <c r="G50">
         <v>16.6</v>
@@ -5387,28 +5387,28 @@
         <v>23.36666666666667</v>
       </c>
       <c r="M50">
-        <v>4.2762384</v>
+        <v>4.365326700000001</v>
       </c>
       <c r="N50">
-        <v>19.09042826666667</v>
+        <v>19.00133996666667</v>
       </c>
       <c r="O50">
-        <v>5.154415632</v>
+        <v>5.130361791</v>
       </c>
       <c r="P50">
-        <v>13.93601263466667</v>
+        <v>13.87097817566667</v>
       </c>
       <c r="Q50">
-        <v>15.23601263466667</v>
+        <v>15.17097817566667</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.2200211833782862</v>
+        <v>0.2228862502365742</v>
       </c>
       <c r="T50">
-        <v>2.087124884347369</v>
+        <v>2.121447647052224</v>
       </c>
       <c r="U50">
         <v>0.0553</v>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>5.464304016975916</v>
+        <v>5.352787608466203</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1334527976206529</v>
+        <v>0.1331174598845969</v>
       </c>
       <c r="C51">
-        <v>97.48302682898735</v>
+        <v>96.48581422866144</v>
       </c>
       <c r="D51">
-        <v>159.8220268289874</v>
+        <v>160.4358142286615</v>
       </c>
       <c r="E51">
-        <v>-36.56100000000001</v>
+        <v>-34.95</v>
       </c>
       <c r="F51">
-        <v>78.93900000000001</v>
+        <v>80.55000000000001</v>
       </c>
       <c r="G51">
         <v>16.6</v>
@@ -5469,28 +5469,28 @@
         <v>23.36666666666667</v>
       </c>
       <c r="M51">
-        <v>4.365326700000001</v>
+        <v>4.454415000000001</v>
       </c>
       <c r="N51">
-        <v>19.00133996666667</v>
+        <v>18.91225166666667</v>
       </c>
       <c r="O51">
-        <v>5.130361791</v>
+        <v>5.106307950000001</v>
       </c>
       <c r="P51">
-        <v>13.87097817566667</v>
+        <v>13.80594371666666</v>
       </c>
       <c r="Q51">
-        <v>15.17097817566667</v>
+        <v>15.10594371666667</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.2228862502365742</v>
+        <v>0.2258659197691938</v>
       </c>
       <c r="T51">
-        <v>2.121447647052224</v>
+        <v>2.157143320265273</v>
       </c>
       <c r="U51">
         <v>0.0553</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>5.352787608466203</v>
+        <v>5.245731856296879</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1331174598845969</v>
+        <v>0.1327821221485409</v>
       </c>
       <c r="C52">
-        <v>96.48581422866144</v>
+        <v>95.49333423480543</v>
       </c>
       <c r="D52">
-        <v>160.4358142286615</v>
+        <v>161.0543342348055</v>
       </c>
       <c r="E52">
-        <v>-34.95</v>
+        <v>-33.339</v>
       </c>
       <c r="F52">
-        <v>80.55000000000001</v>
+        <v>82.16100000000002</v>
       </c>
       <c r="G52">
         <v>16.6</v>
@@ -5551,28 +5551,28 @@
         <v>23.36666666666667</v>
       </c>
       <c r="M52">
-        <v>4.454415000000001</v>
+        <v>4.543503300000001</v>
       </c>
       <c r="N52">
-        <v>18.91225166666667</v>
+        <v>18.82316336666667</v>
       </c>
       <c r="O52">
-        <v>5.106307950000001</v>
+        <v>5.082254109</v>
       </c>
       <c r="P52">
-        <v>13.80594371666666</v>
+        <v>13.74090925766667</v>
       </c>
       <c r="Q52">
-        <v>15.10594371666667</v>
+        <v>15.04090925766667</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.2258659197691938</v>
+        <v>0.2289672084664101</v>
       </c>
       <c r="T52">
-        <v>2.157143320265273</v>
+        <v>2.194295959731916</v>
       </c>
       <c r="U52">
         <v>0.0553</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>5.245731856296879</v>
+        <v>5.142874368918509</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1327821221485409</v>
+        <v>0.1324467844124849</v>
       </c>
       <c r="C53">
-        <v>95.49333423480543</v>
+        <v>94.50564179538605</v>
       </c>
       <c r="D53">
-        <v>161.0543342348055</v>
+        <v>161.6776417953861</v>
       </c>
       <c r="E53">
-        <v>-33.339</v>
+        <v>-31.72799999999999</v>
       </c>
       <c r="F53">
-        <v>82.16100000000002</v>
+        <v>83.77200000000002</v>
       </c>
       <c r="G53">
         <v>16.6</v>
@@ -5633,28 +5633,28 @@
         <v>23.36666666666667</v>
       </c>
       <c r="M53">
-        <v>4.543503300000001</v>
+        <v>4.632591600000001</v>
       </c>
       <c r="N53">
-        <v>18.82316336666667</v>
+        <v>18.73407506666667</v>
       </c>
       <c r="O53">
-        <v>5.082254109</v>
+        <v>5.058200268</v>
       </c>
       <c r="P53">
-        <v>13.74090925766667</v>
+        <v>13.67587479866667</v>
       </c>
       <c r="Q53">
-        <v>15.04090925766667</v>
+        <v>14.97587479866667</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.2289672084664101</v>
+        <v>0.2321977175260103</v>
       </c>
       <c r="T53">
-        <v>2.194295959731916</v>
+        <v>2.232996625843001</v>
       </c>
       <c r="U53">
         <v>0.0553</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>5.142874368918509</v>
+        <v>5.043972938746998</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1324467844124849</v>
+        <v>0.132111446676429</v>
       </c>
       <c r="C54">
-        <v>94.50564179538605</v>
+        <v>93.52279271230654</v>
       </c>
       <c r="D54">
-        <v>161.6776417953861</v>
+        <v>162.3057927123066</v>
       </c>
       <c r="E54">
-        <v>-31.72799999999999</v>
+        <v>-30.117</v>
       </c>
       <c r="F54">
-        <v>83.77200000000002</v>
+        <v>85.38300000000001</v>
       </c>
       <c r="G54">
         <v>16.6</v>
@@ -5715,28 +5715,28 @@
         <v>23.36666666666667</v>
       </c>
       <c r="M54">
-        <v>4.632591600000001</v>
+        <v>4.721679900000001</v>
       </c>
       <c r="N54">
-        <v>18.73407506666667</v>
+        <v>18.64498676666667</v>
       </c>
       <c r="O54">
-        <v>5.058200268</v>
+        <v>5.034146427</v>
       </c>
       <c r="P54">
-        <v>13.67587479866667</v>
+        <v>13.61084033966667</v>
       </c>
       <c r="Q54">
-        <v>14.97587479866667</v>
+        <v>14.91084033966667</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.2321977175260103</v>
+        <v>0.2355656950562319</v>
       </c>
       <c r="T54">
-        <v>2.232996625843001</v>
+        <v>2.273344128809879</v>
       </c>
       <c r="U54">
         <v>0.0553</v>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>5.043972938746998</v>
+        <v>4.948803638015923</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.132111446676429</v>
+        <v>0.131776108940373</v>
       </c>
       <c r="C55">
-        <v>93.52279271230654</v>
+        <v>92.54484365806009</v>
       </c>
       <c r="D55">
-        <v>162.3057927123066</v>
+        <v>162.9388436580601</v>
       </c>
       <c r="E55">
-        <v>-30.117</v>
+        <v>-28.506</v>
       </c>
       <c r="F55">
-        <v>85.38300000000001</v>
+        <v>86.99400000000001</v>
       </c>
       <c r="G55">
         <v>16.6</v>
@@ -5797,28 +5797,28 @@
         <v>23.36666666666667</v>
       </c>
       <c r="M55">
-        <v>4.721679900000001</v>
+        <v>4.810768200000001</v>
       </c>
       <c r="N55">
-        <v>18.64498676666667</v>
+        <v>18.55589846666667</v>
       </c>
       <c r="O55">
-        <v>5.034146427</v>
+        <v>5.010092586</v>
       </c>
       <c r="P55">
-        <v>13.61084033966667</v>
+        <v>13.54580588066667</v>
       </c>
       <c r="Q55">
-        <v>14.91084033966667</v>
+        <v>14.84580588066667</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.2355656950562319</v>
+        <v>0.2390801063921153</v>
       </c>
       <c r="T55">
-        <v>2.273344128809879</v>
+        <v>2.315445871036185</v>
       </c>
       <c r="U55">
         <v>0.0553</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>4.948803638015923</v>
+        <v>4.857159126200814</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.131776108940373</v>
+        <v>0.1314407712043171</v>
       </c>
       <c r="C56">
-        <v>92.54484365806009</v>
+        <v>91.57185219277437</v>
       </c>
       <c r="D56">
-        <v>162.9388436580601</v>
+        <v>163.5768521927744</v>
       </c>
       <c r="E56">
-        <v>-28.506</v>
+        <v>-26.895</v>
       </c>
       <c r="F56">
-        <v>86.99400000000001</v>
+        <v>88.60500000000002</v>
       </c>
       <c r="G56">
         <v>16.6</v>
@@ -5879,28 +5879,28 @@
         <v>23.36666666666667</v>
       </c>
       <c r="M56">
-        <v>4.810768200000001</v>
+        <v>4.899856500000001</v>
       </c>
       <c r="N56">
-        <v>18.55589846666667</v>
+        <v>18.46681016666667</v>
       </c>
       <c r="O56">
-        <v>5.010092586</v>
+        <v>4.986038745</v>
       </c>
       <c r="P56">
-        <v>13.54580588066667</v>
+        <v>13.48077142166666</v>
       </c>
       <c r="Q56">
-        <v>14.84580588066667</v>
+        <v>14.78077142166667</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.2390801063921153</v>
+        <v>0.2427507137873713</v>
       </c>
       <c r="T56">
-        <v>2.315445871036185</v>
+        <v>2.359418801805883</v>
       </c>
       <c r="U56">
         <v>0.0553</v>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>4.857159126200814</v>
+        <v>4.768847142088072</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1314407712043171</v>
+        <v>0.1311054334682611</v>
       </c>
       <c r="C57">
-        <v>91.57185219277437</v>
+        <v>90.60387678165826</v>
       </c>
       <c r="D57">
-        <v>163.5768521927744</v>
+        <v>164.2198767816583</v>
       </c>
       <c r="E57">
-        <v>-26.895</v>
+        <v>-25.28399999999999</v>
       </c>
       <c r="F57">
-        <v>88.60500000000002</v>
+        <v>90.21600000000002</v>
       </c>
       <c r="G57">
         <v>16.6</v>
@@ -5961,28 +5961,28 @@
         <v>23.36666666666667</v>
       </c>
       <c r="M57">
-        <v>4.899856500000001</v>
+        <v>4.988944800000001</v>
       </c>
       <c r="N57">
-        <v>18.46681016666667</v>
+        <v>18.37772186666666</v>
       </c>
       <c r="O57">
-        <v>4.986038745</v>
+        <v>4.961984903999999</v>
       </c>
       <c r="P57">
-        <v>13.48077142166666</v>
+        <v>13.41573696266667</v>
       </c>
       <c r="Q57">
-        <v>14.78077142166667</v>
+        <v>14.71573696266667</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.2427507137873713</v>
+        <v>0.2465881669733207</v>
       </c>
       <c r="T57">
-        <v>2.359418801805883</v>
+        <v>2.405390502156021</v>
       </c>
       <c r="U57">
         <v>0.0553</v>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>4.768847142088072</v>
+        <v>4.683689157407928</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1311054334682611</v>
+        <v>0.1307700957322051</v>
       </c>
       <c r="C58">
-        <v>90.60387678165826</v>
+        <v>89.64097681286108</v>
       </c>
       <c r="D58">
-        <v>164.2198767816583</v>
+        <v>164.8679768128611</v>
       </c>
       <c r="E58">
-        <v>-25.28399999999999</v>
+        <v>-23.67299999999999</v>
       </c>
       <c r="F58">
-        <v>90.21600000000002</v>
+        <v>91.82700000000003</v>
       </c>
       <c r="G58">
         <v>16.6</v>
@@ -6043,28 +6043,28 @@
         <v>23.36666666666667</v>
       </c>
       <c r="M58">
-        <v>4.988944800000001</v>
+        <v>5.078033100000002</v>
       </c>
       <c r="N58">
-        <v>18.37772186666666</v>
+        <v>18.28863356666666</v>
       </c>
       <c r="O58">
-        <v>4.961984903999999</v>
+        <v>4.937931063</v>
       </c>
       <c r="P58">
-        <v>13.41573696266667</v>
+        <v>13.35070250366666</v>
       </c>
       <c r="Q58">
-        <v>14.71573696266667</v>
+        <v>14.65070250366666</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.2465881669733207</v>
+        <v>0.2506041063539655</v>
       </c>
       <c r="T58">
-        <v>2.405390502156021</v>
+        <v>2.453500421127097</v>
       </c>
       <c r="U58">
         <v>0.0553</v>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>4.683689157407928</v>
+        <v>4.601519172190244</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1307700957322051</v>
+        <v>0.1304347579961491</v>
       </c>
       <c r="C59">
-        <v>89.64097681286108</v>
+        <v>88.68321261575745</v>
       </c>
       <c r="D59">
-        <v>164.8679768128611</v>
+        <v>165.5212126157575</v>
       </c>
       <c r="E59">
-        <v>-23.67299999999999</v>
+        <v>-22.06199999999998</v>
       </c>
       <c r="F59">
-        <v>91.82700000000003</v>
+        <v>93.43800000000003</v>
       </c>
       <c r="G59">
         <v>16.6</v>
@@ -6125,28 +6125,28 @@
         <v>23.36666666666667</v>
       </c>
       <c r="M59">
-        <v>5.078033100000002</v>
+        <v>5.167121400000002</v>
       </c>
       <c r="N59">
-        <v>18.28863356666666</v>
+        <v>18.19954526666666</v>
       </c>
       <c r="O59">
-        <v>4.937931063</v>
+        <v>4.913877222</v>
       </c>
       <c r="P59">
-        <v>13.35070250366666</v>
+        <v>13.28566804466666</v>
       </c>
       <c r="Q59">
-        <v>14.65070250366666</v>
+        <v>14.58566804466667</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.2506041063539655</v>
+        <v>0.2548112809432123</v>
       </c>
       <c r="T59">
-        <v>2.453500421127097</v>
+        <v>2.503901288620605</v>
       </c>
       <c r="U59">
         <v>0.0553</v>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>4.601519172190244</v>
+        <v>4.522182634738687</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1304347579961491</v>
+        <v>0.1311761702600932</v>
       </c>
       <c r="C60">
-        <v>88.68321261575748</v>
+        <v>85.63481554579806</v>
       </c>
       <c r="D60">
-        <v>165.5212126157575</v>
+        <v>164.0838155457981</v>
       </c>
       <c r="E60">
-        <v>-22.06200000000001</v>
+        <v>-20.45100000000001</v>
       </c>
       <c r="F60">
-        <v>93.438</v>
+        <v>95.04900000000001</v>
       </c>
       <c r="G60">
         <v>16.6</v>
@@ -6207,45 +6207,45 @@
         <v>23.36666666666667</v>
       </c>
       <c r="M60">
-        <v>5.1671214</v>
+        <v>5.493832200000001</v>
       </c>
       <c r="N60">
-        <v>18.19954526666667</v>
+        <v>17.87283446666667</v>
       </c>
       <c r="O60">
-        <v>4.913877222000001</v>
+        <v>4.825665306</v>
       </c>
       <c r="P60">
-        <v>13.28566804466667</v>
+        <v>13.04716916066667</v>
       </c>
       <c r="Q60">
-        <v>14.58566804466667</v>
+        <v>14.34716916066667</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.2548112809432122</v>
+        <v>0.2592236835612029</v>
       </c>
       <c r="T60">
-        <v>2.503901288620603</v>
+        <v>2.556760735016234</v>
       </c>
       <c r="U60">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V60">
         <v>0.27</v>
       </c>
       <c r="W60">
-        <v>0.040369</v>
+        <v>0.042194</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y60">
-        <v>4.52218263473869</v>
+        <v>4.253254525441578</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1311761702600932</v>
+        <v>0.1308590825240372</v>
       </c>
       <c r="C61">
-        <v>85.63481554579806</v>
+        <v>84.63549585142734</v>
       </c>
       <c r="D61">
-        <v>164.0838155457981</v>
+        <v>164.6954958514274</v>
       </c>
       <c r="E61">
-        <v>-20.45100000000001</v>
+        <v>-18.84</v>
       </c>
       <c r="F61">
-        <v>95.04900000000001</v>
+        <v>96.66000000000001</v>
       </c>
       <c r="G61">
         <v>16.6</v>
@@ -6289,28 +6289,28 @@
         <v>23.36666666666667</v>
       </c>
       <c r="M61">
-        <v>5.493832200000001</v>
+        <v>5.586948000000001</v>
       </c>
       <c r="N61">
-        <v>17.87283446666667</v>
+        <v>17.77971866666667</v>
       </c>
       <c r="O61">
-        <v>4.825665306</v>
+        <v>4.800524040000001</v>
       </c>
       <c r="P61">
-        <v>13.04716916066667</v>
+        <v>12.97919462666667</v>
       </c>
       <c r="Q61">
-        <v>14.34716916066667</v>
+        <v>14.27919462666667</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.2592236835612029</v>
+        <v>0.263856706310093</v>
       </c>
       <c r="T61">
-        <v>2.556760735016234</v>
+        <v>2.612263153731645</v>
       </c>
       <c r="U61">
         <v>0.0578</v>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>4.253254525441578</v>
+        <v>4.182366950017553</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1308590825240372</v>
+        <v>0.1305419947879813</v>
       </c>
       <c r="C62">
-        <v>84.63549585142734</v>
+        <v>83.64075372981216</v>
       </c>
       <c r="D62">
-        <v>164.6954958514274</v>
+        <v>165.3117537298122</v>
       </c>
       <c r="E62">
-        <v>-18.84</v>
+        <v>-17.229</v>
       </c>
       <c r="F62">
-        <v>96.66000000000001</v>
+        <v>98.27100000000002</v>
       </c>
       <c r="G62">
         <v>16.6</v>
@@ -6371,28 +6371,28 @@
         <v>23.36666666666667</v>
       </c>
       <c r="M62">
-        <v>5.586948000000001</v>
+        <v>5.680063800000001</v>
       </c>
       <c r="N62">
-        <v>17.77971866666667</v>
+        <v>17.68660286666667</v>
       </c>
       <c r="O62">
-        <v>4.800524040000001</v>
+        <v>4.775382774000001</v>
       </c>
       <c r="P62">
-        <v>12.97919462666667</v>
+        <v>12.91122009266667</v>
       </c>
       <c r="Q62">
-        <v>14.27919462666667</v>
+        <v>14.21122009266667</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.263856706310093</v>
+        <v>0.2687273199691827</v>
       </c>
       <c r="T62">
-        <v>2.612263153731645</v>
+        <v>2.670611850329898</v>
       </c>
       <c r="U62">
         <v>0.0578</v>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>4.182366950017553</v>
+        <v>4.113803557394315</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1305419947879813</v>
+        <v>0.1302249070519253</v>
       </c>
       <c r="C63">
-        <v>83.64075372981216</v>
+        <v>82.65064075905569</v>
       </c>
       <c r="D63">
-        <v>165.3117537298122</v>
+        <v>165.9326407590557</v>
       </c>
       <c r="E63">
-        <v>-17.229</v>
+        <v>-15.61799999999999</v>
       </c>
       <c r="F63">
-        <v>98.27100000000002</v>
+        <v>99.88200000000002</v>
       </c>
       <c r="G63">
         <v>16.6</v>
@@ -6453,28 +6453,28 @@
         <v>23.36666666666667</v>
       </c>
       <c r="M63">
-        <v>5.680063800000001</v>
+        <v>5.773179600000002</v>
       </c>
       <c r="N63">
-        <v>17.68660286666667</v>
+        <v>17.59348706666666</v>
       </c>
       <c r="O63">
-        <v>4.775382774000001</v>
+        <v>4.750241508</v>
       </c>
       <c r="P63">
-        <v>12.91122009266667</v>
+        <v>12.84324555866666</v>
       </c>
       <c r="Q63">
-        <v>14.21122009266667</v>
+        <v>14.14324555866667</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.2687273199691827</v>
+        <v>0.2738542817155928</v>
       </c>
       <c r="T63">
-        <v>2.670611850329898</v>
+        <v>2.732031530959638</v>
       </c>
       <c r="U63">
         <v>0.0578</v>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>4.113803557394315</v>
+        <v>4.047451887113759</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1302249070519253</v>
+        <v>0.1315174693158693</v>
       </c>
       <c r="C64">
-        <v>82.65064075905569</v>
+        <v>78.53748721306867</v>
       </c>
       <c r="D64">
-        <v>165.9326407590557</v>
+        <v>163.4304872130687</v>
       </c>
       <c r="E64">
-        <v>-15.61799999999999</v>
+        <v>-14.00700000000001</v>
       </c>
       <c r="F64">
-        <v>99.88200000000002</v>
+        <v>101.493</v>
       </c>
       <c r="G64">
         <v>16.6</v>
@@ -6535,45 +6535,45 @@
         <v>23.36666666666667</v>
       </c>
       <c r="M64">
-        <v>5.773179600000002</v>
+        <v>6.221520900000001</v>
       </c>
       <c r="N64">
-        <v>17.59348706666666</v>
+        <v>17.14514576666667</v>
       </c>
       <c r="O64">
-        <v>4.750241508</v>
+        <v>4.629189357</v>
       </c>
       <c r="P64">
-        <v>12.84324555866666</v>
+        <v>12.51595640966666</v>
       </c>
       <c r="Q64">
-        <v>14.14324555866667</v>
+        <v>13.81595640966666</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.2738542817155928</v>
+        <v>0.2792583765293765</v>
       </c>
       <c r="T64">
-        <v>2.732031530959638</v>
+        <v>2.79677119432612</v>
       </c>
       <c r="U64">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V64">
         <v>0.27</v>
       </c>
       <c r="W64">
-        <v>0.042194</v>
+        <v>0.044749</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y64">
-        <v>4.047451887113759</v>
+        <v>3.755780466262946</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1315174693158693</v>
+        <v>0.1312259315798134</v>
       </c>
       <c r="C65">
-        <v>78.53748721306867</v>
+        <v>77.48423535070651</v>
       </c>
       <c r="D65">
-        <v>163.4304872130687</v>
+        <v>163.9882353507065</v>
       </c>
       <c r="E65">
-        <v>-14.00700000000001</v>
+        <v>-12.396</v>
       </c>
       <c r="F65">
-        <v>101.493</v>
+        <v>103.104</v>
       </c>
       <c r="G65">
         <v>16.6</v>
@@ -6617,28 +6617,28 @@
         <v>23.36666666666667</v>
       </c>
       <c r="M65">
-        <v>6.221520900000001</v>
+        <v>6.320275200000001</v>
       </c>
       <c r="N65">
-        <v>17.14514576666667</v>
+        <v>17.04639146666667</v>
       </c>
       <c r="O65">
-        <v>4.629189357</v>
+        <v>4.602525696</v>
       </c>
       <c r="P65">
-        <v>12.51595640966666</v>
+        <v>12.44386577066667</v>
       </c>
       <c r="Q65">
-        <v>13.81595640966666</v>
+        <v>13.74386577066667</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.2792583765293765</v>
+        <v>0.2849626988328149</v>
       </c>
       <c r="T65">
-        <v>2.79677119432612</v>
+        <v>2.865107505657408</v>
       </c>
       <c r="U65">
         <v>0.0613</v>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>3.755780466262946</v>
+        <v>3.697096396477587</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1312259315798134</v>
+        <v>0.1309343938437574</v>
       </c>
       <c r="C66">
-        <v>77.48423535070651</v>
+        <v>76.43480343988209</v>
       </c>
       <c r="D66">
-        <v>163.9882353507065</v>
+        <v>164.5498034398821</v>
       </c>
       <c r="E66">
-        <v>-12.396</v>
+        <v>-10.785</v>
       </c>
       <c r="F66">
-        <v>103.104</v>
+        <v>104.715</v>
       </c>
       <c r="G66">
         <v>16.6</v>
@@ -6699,28 +6699,28 @@
         <v>23.36666666666667</v>
       </c>
       <c r="M66">
-        <v>6.320275200000001</v>
+        <v>6.419029500000001</v>
       </c>
       <c r="N66">
-        <v>17.04639146666667</v>
+        <v>16.94763716666667</v>
       </c>
       <c r="O66">
-        <v>4.602525696</v>
+        <v>4.575862035</v>
       </c>
       <c r="P66">
-        <v>12.44386577066667</v>
+        <v>12.37177513166667</v>
       </c>
       <c r="Q66">
-        <v>13.74386577066667</v>
+        <v>13.67177513166667</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.2849626988328149</v>
+        <v>0.2909929824107354</v>
       </c>
       <c r="T66">
-        <v>2.865107505657408</v>
+        <v>2.937348749064769</v>
       </c>
       <c r="U66">
         <v>0.0613</v>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>3.697096396477587</v>
+        <v>3.640217990377932</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1309343938437574</v>
+        <v>0.1306428561077014</v>
       </c>
       <c r="C67">
-        <v>76.43480343988209</v>
+        <v>75.38923085904418</v>
       </c>
       <c r="D67">
-        <v>164.5498034398821</v>
+        <v>165.1152308590442</v>
       </c>
       <c r="E67">
-        <v>-10.785</v>
+        <v>-9.173999999999992</v>
       </c>
       <c r="F67">
-        <v>104.715</v>
+        <v>106.326</v>
       </c>
       <c r="G67">
         <v>16.6</v>
@@ -6781,28 +6781,28 @@
         <v>23.36666666666667</v>
       </c>
       <c r="M67">
-        <v>6.419029500000001</v>
+        <v>6.517783800000001</v>
       </c>
       <c r="N67">
-        <v>16.94763716666667</v>
+        <v>16.84888286666667</v>
       </c>
       <c r="O67">
-        <v>4.575862035</v>
+        <v>4.549198374</v>
       </c>
       <c r="P67">
-        <v>12.37177513166667</v>
+        <v>12.29968449266667</v>
       </c>
       <c r="Q67">
-        <v>13.67177513166667</v>
+        <v>13.59968449266667</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2909929824107354</v>
+        <v>0.297377988552063</v>
       </c>
       <c r="T67">
-        <v>2.937348749064769</v>
+        <v>3.013839477378444</v>
       </c>
       <c r="U67">
         <v>0.0613</v>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>3.640217990377932</v>
+        <v>3.585063172341903</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1306428561077014</v>
+        <v>0.1303513183716455</v>
       </c>
       <c r="C68">
-        <v>75.38923085904418</v>
+        <v>74.34755752975808</v>
       </c>
       <c r="D68">
-        <v>165.1152308590442</v>
+        <v>165.6845575297581</v>
       </c>
       <c r="E68">
-        <v>-9.173999999999992</v>
+        <v>-7.562999999999988</v>
       </c>
       <c r="F68">
-        <v>106.326</v>
+        <v>107.937</v>
       </c>
       <c r="G68">
         <v>16.6</v>
@@ -6863,28 +6863,28 @@
         <v>23.36666666666667</v>
       </c>
       <c r="M68">
-        <v>6.517783800000001</v>
+        <v>6.616538100000001</v>
       </c>
       <c r="N68">
-        <v>16.84888286666667</v>
+        <v>16.75012856666667</v>
       </c>
       <c r="O68">
-        <v>4.549198374</v>
+        <v>4.522534713000001</v>
       </c>
       <c r="P68">
-        <v>12.29968449266667</v>
+        <v>12.22759385366667</v>
       </c>
       <c r="Q68">
-        <v>13.59968449266667</v>
+        <v>13.52759385366667</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.297377988552063</v>
+        <v>0.304149964762562</v>
       </c>
       <c r="T68">
-        <v>3.013839477378444</v>
+        <v>3.094966007408101</v>
       </c>
       <c r="U68">
         <v>0.0613</v>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>3.585063172341903</v>
+        <v>3.531554766784561</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1303513183716455</v>
+        <v>0.1314497006355895</v>
       </c>
       <c r="C69">
-        <v>74.34755752975808</v>
+        <v>70.61179844654319</v>
       </c>
       <c r="D69">
-        <v>165.6845575297581</v>
+        <v>163.5597984465432</v>
       </c>
       <c r="E69">
-        <v>-7.562999999999988</v>
+        <v>-5.951999999999984</v>
       </c>
       <c r="F69">
-        <v>107.937</v>
+        <v>109.548</v>
       </c>
       <c r="G69">
         <v>16.6</v>
@@ -6945,45 +6945,45 @@
         <v>23.36666666666667</v>
       </c>
       <c r="M69">
-        <v>6.616538100000001</v>
+        <v>7.022026800000003</v>
       </c>
       <c r="N69">
-        <v>16.75012856666667</v>
+        <v>16.34463986666666</v>
       </c>
       <c r="O69">
-        <v>4.522534713000001</v>
+        <v>4.413052764</v>
       </c>
       <c r="P69">
-        <v>12.22759385366667</v>
+        <v>11.93158710266666</v>
       </c>
       <c r="Q69">
-        <v>13.52759385366667</v>
+        <v>13.23158710266667</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.304149964762562</v>
+        <v>0.3113451894862172</v>
       </c>
       <c r="T69">
-        <v>3.094966007408101</v>
+        <v>3.181162945564612</v>
       </c>
       <c r="U69">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V69">
         <v>0.27</v>
       </c>
       <c r="W69">
-        <v>0.044749</v>
+        <v>0.046793</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y69">
-        <v>3.531554766784561</v>
+        <v>3.32762425040398</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1314497006355895</v>
+        <v>0.1311786028995335</v>
       </c>
       <c r="C70">
-        <v>70.61179844654319</v>
+        <v>69.52014040767614</v>
       </c>
       <c r="D70">
-        <v>163.5597984465432</v>
+        <v>164.0791404076762</v>
       </c>
       <c r="E70">
-        <v>-5.951999999999984</v>
+        <v>-4.340999999999994</v>
       </c>
       <c r="F70">
-        <v>109.548</v>
+        <v>111.159</v>
       </c>
       <c r="G70">
         <v>16.6</v>
@@ -7027,28 +7027,28 @@
         <v>23.36666666666667</v>
       </c>
       <c r="M70">
-        <v>7.022026800000003</v>
+        <v>7.125291900000001</v>
       </c>
       <c r="N70">
-        <v>16.34463986666666</v>
+        <v>16.24137476666667</v>
       </c>
       <c r="O70">
-        <v>4.413052764</v>
+        <v>4.385171187</v>
       </c>
       <c r="P70">
-        <v>11.93158710266666</v>
+        <v>11.85620357966667</v>
       </c>
       <c r="Q70">
-        <v>13.23158710266667</v>
+        <v>13.15620357966667</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.3113451894862172</v>
+        <v>0.3190046222565597</v>
       </c>
       <c r="T70">
-        <v>3.181162945564612</v>
+        <v>3.272920976505412</v>
       </c>
       <c r="U70">
         <v>0.0641</v>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>3.32762425040398</v>
+        <v>3.279397811992329</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1311786028995335</v>
+        <v>0.1309075051634776</v>
       </c>
       <c r="C71">
-        <v>69.52014040767614</v>
+        <v>68.43179094728582</v>
       </c>
       <c r="D71">
-        <v>164.0791404076762</v>
+        <v>164.6017909472858</v>
       </c>
       <c r="E71">
-        <v>-4.340999999999994</v>
+        <v>-2.72999999999999</v>
       </c>
       <c r="F71">
-        <v>111.159</v>
+        <v>112.77</v>
       </c>
       <c r="G71">
         <v>16.6</v>
@@ -7109,28 +7109,28 @@
         <v>23.36666666666667</v>
       </c>
       <c r="M71">
-        <v>7.125291900000001</v>
+        <v>7.228557000000002</v>
       </c>
       <c r="N71">
-        <v>16.24137476666667</v>
+        <v>16.13810966666667</v>
       </c>
       <c r="O71">
-        <v>4.385171187</v>
+        <v>4.35728961</v>
       </c>
       <c r="P71">
-        <v>11.85620357966667</v>
+        <v>11.78082005666667</v>
       </c>
       <c r="Q71">
-        <v>13.15620357966667</v>
+        <v>13.08082005666667</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.3190046222565597</v>
+        <v>0.3271746838782586</v>
       </c>
       <c r="T71">
-        <v>3.272920976505412</v>
+        <v>3.370796209508934</v>
       </c>
       <c r="U71">
         <v>0.0641</v>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>3.279397811992329</v>
+        <v>3.232549271821009</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1309075051634776</v>
+        <v>0.1306364074274216</v>
       </c>
       <c r="C72">
-        <v>68.43179094728582</v>
+        <v>67.34678178341051</v>
       </c>
       <c r="D72">
-        <v>164.6017909472858</v>
+        <v>165.1277817834105</v>
       </c>
       <c r="E72">
-        <v>-2.72999999999999</v>
+        <v>-1.118999999999986</v>
       </c>
       <c r="F72">
-        <v>112.77</v>
+        <v>114.381</v>
       </c>
       <c r="G72">
         <v>16.6</v>
@@ -7191,28 +7191,28 @@
         <v>23.36666666666667</v>
       </c>
       <c r="M72">
-        <v>7.228557000000002</v>
+        <v>7.331822100000002</v>
       </c>
       <c r="N72">
-        <v>16.13810966666667</v>
+        <v>16.03484456666666</v>
       </c>
       <c r="O72">
-        <v>4.35728961</v>
+        <v>4.329408032999999</v>
       </c>
       <c r="P72">
-        <v>11.78082005666667</v>
+        <v>11.70543653366666</v>
       </c>
       <c r="Q72">
-        <v>13.08082005666667</v>
+        <v>13.00543653366666</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.3271746838782586</v>
+        <v>0.3359081980255918</v>
       </c>
       <c r="T72">
-        <v>3.370796209508934</v>
+        <v>3.475421458581663</v>
       </c>
       <c r="U72">
         <v>0.0641</v>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>3.232549271821009</v>
+        <v>3.187020408837615</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1306364074274216</v>
+        <v>0.1303653096913656</v>
       </c>
       <c r="C73">
-        <v>67.34678178341052</v>
+        <v>66.26514504081248</v>
       </c>
       <c r="D73">
-        <v>165.1277817834105</v>
+        <v>165.6571450408125</v>
       </c>
       <c r="E73">
-        <v>-1.119</v>
+        <v>0.4920000000000044</v>
       </c>
       <c r="F73">
-        <v>114.381</v>
+        <v>115.992</v>
       </c>
       <c r="G73">
         <v>16.6</v>
@@ -7273,28 +7273,28 @@
         <v>23.36666666666667</v>
       </c>
       <c r="M73">
-        <v>7.331822100000001</v>
+        <v>7.435087200000002</v>
       </c>
       <c r="N73">
-        <v>16.03484456666667</v>
+        <v>15.93157946666667</v>
       </c>
       <c r="O73">
-        <v>4.329408033</v>
+        <v>4.301526456</v>
       </c>
       <c r="P73">
-        <v>11.70543653366667</v>
+        <v>11.63005301066666</v>
       </c>
       <c r="Q73">
-        <v>13.00543653366667</v>
+        <v>12.93005301066666</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.3359081980255917</v>
+        <v>0.3452655346120201</v>
       </c>
       <c r="T73">
-        <v>3.475421458581662</v>
+        <v>3.587519939731015</v>
       </c>
       <c r="U73">
         <v>0.0641</v>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>3.187020408837616</v>
+        <v>3.142756236492648</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1303653096913656</v>
+        <v>0.1300942119553096</v>
       </c>
       <c r="C74">
-        <v>66.26514504081248</v>
+        <v>65.18691325751848</v>
       </c>
       <c r="D74">
-        <v>165.6571450408125</v>
+        <v>166.1899132575185</v>
       </c>
       <c r="E74">
-        <v>0.4920000000000044</v>
+        <v>2.102999999999994</v>
       </c>
       <c r="F74">
-        <v>115.992</v>
+        <v>117.603</v>
       </c>
       <c r="G74">
         <v>16.6</v>
@@ -7355,28 +7355,28 @@
         <v>23.36666666666667</v>
       </c>
       <c r="M74">
-        <v>7.435087200000002</v>
+        <v>7.538352300000001</v>
       </c>
       <c r="N74">
-        <v>15.93157946666667</v>
+        <v>15.82831436666667</v>
       </c>
       <c r="O74">
-        <v>4.301526456</v>
+        <v>4.273644879</v>
       </c>
       <c r="P74">
-        <v>11.63005301066666</v>
+        <v>11.55466948766666</v>
       </c>
       <c r="Q74">
-        <v>12.93005301066666</v>
+        <v>12.85466948766667</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.3452655346120201</v>
+        <v>0.3553160072418876</v>
       </c>
       <c r="T74">
-        <v>3.587519939731015</v>
+        <v>3.707922012076616</v>
       </c>
       <c r="U74">
         <v>0.0641</v>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>3.142756236492648</v>
+        <v>3.099704781198228</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1300942119553096</v>
+        <v>0.1298231142192537</v>
       </c>
       <c r="C75">
-        <v>65.18691325751848</v>
+        <v>64.11211939148636</v>
       </c>
       <c r="D75">
-        <v>166.1899132575185</v>
+        <v>166.7261193914864</v>
       </c>
       <c r="E75">
-        <v>2.102999999999994</v>
+        <v>3.713999999999999</v>
       </c>
       <c r="F75">
-        <v>117.603</v>
+        <v>119.214</v>
       </c>
       <c r="G75">
         <v>16.6</v>
@@ -7437,28 +7437,28 @@
         <v>23.36666666666667</v>
       </c>
       <c r="M75">
-        <v>7.538352300000001</v>
+        <v>7.641617400000001</v>
       </c>
       <c r="N75">
-        <v>15.82831436666667</v>
+        <v>15.72504926666667</v>
       </c>
       <c r="O75">
-        <v>4.273644879</v>
+        <v>4.245763302</v>
       </c>
       <c r="P75">
-        <v>11.55466948766666</v>
+        <v>11.47928596466667</v>
       </c>
       <c r="Q75">
-        <v>12.85466948766667</v>
+        <v>12.77928596466667</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.3553160072418876</v>
+        <v>0.3661395931509757</v>
       </c>
       <c r="T75">
-        <v>3.707922012076616</v>
+        <v>3.837585782294956</v>
       </c>
       <c r="U75">
         <v>0.0641</v>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>3.099704781198228</v>
+        <v>3.057816878749604</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1298231142192537</v>
+        <v>0.1295520164831977</v>
       </c>
       <c r="C76">
-        <v>64.11211939148636</v>
+        <v>63.04079682740212</v>
       </c>
       <c r="D76">
-        <v>166.7261193914864</v>
+        <v>167.2657968274021</v>
       </c>
       <c r="E76">
-        <v>3.713999999999999</v>
+        <v>5.325000000000003</v>
       </c>
       <c r="F76">
-        <v>119.214</v>
+        <v>120.825</v>
       </c>
       <c r="G76">
         <v>16.6</v>
@@ -7519,28 +7519,28 @@
         <v>23.36666666666667</v>
       </c>
       <c r="M76">
-        <v>7.641617400000001</v>
+        <v>7.744882500000002</v>
       </c>
       <c r="N76">
-        <v>15.72504926666667</v>
+        <v>15.62178416666666</v>
       </c>
       <c r="O76">
-        <v>4.245763302</v>
+        <v>4.217881725</v>
       </c>
       <c r="P76">
-        <v>11.47928596466667</v>
+        <v>11.40390244166666</v>
       </c>
       <c r="Q76">
-        <v>12.77928596466667</v>
+        <v>12.70390244166667</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.3661395931509757</v>
+        <v>0.3778290659327909</v>
       </c>
       <c r="T76">
-        <v>3.837585782294956</v>
+        <v>3.977622654130763</v>
       </c>
       <c r="U76">
         <v>0.0641</v>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>3.057816878749604</v>
+        <v>3.017045987032942</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1295520164831977</v>
+        <v>0.1336083587471418</v>
       </c>
       <c r="C77">
-        <v>63.04079682740212</v>
+        <v>53.70288642087597</v>
       </c>
       <c r="D77">
-        <v>167.2657968274021</v>
+        <v>159.538886420876</v>
       </c>
       <c r="E77">
-        <v>5.325000000000003</v>
+        <v>6.936000000000007</v>
       </c>
       <c r="F77">
-        <v>120.825</v>
+        <v>122.436</v>
       </c>
       <c r="G77">
         <v>16.6</v>
@@ -7601,45 +7601,45 @@
         <v>23.36666666666667</v>
       </c>
       <c r="M77">
-        <v>7.744882500000002</v>
+        <v>8.803148400000003</v>
       </c>
       <c r="N77">
-        <v>15.62178416666666</v>
+        <v>14.56351826666666</v>
       </c>
       <c r="O77">
-        <v>4.217881725</v>
+        <v>3.932149932</v>
       </c>
       <c r="P77">
-        <v>11.40390244166666</v>
+        <v>10.63136833466666</v>
       </c>
       <c r="Q77">
-        <v>12.70390244166667</v>
+        <v>11.93136833466667</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.3778290659327909</v>
+        <v>0.390492661446424</v>
       </c>
       <c r="T77">
-        <v>3.977622654130763</v>
+        <v>4.129329265286221</v>
       </c>
       <c r="U77">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V77">
         <v>0.27</v>
       </c>
       <c r="W77">
-        <v>0.046793</v>
+        <v>0.05248700000000001</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y77">
-        <v>3.017045987032942</v>
+        <v>2.65435337505689</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1336083587471418</v>
+        <v>0.1333942010110858</v>
       </c>
       <c r="C78">
-        <v>53.70288642087597</v>
+        <v>52.4819406291958</v>
       </c>
       <c r="D78">
-        <v>159.538886420876</v>
+        <v>159.9289406291958</v>
       </c>
       <c r="E78">
-        <v>6.936000000000007</v>
+        <v>8.547000000000011</v>
       </c>
       <c r="F78">
-        <v>122.436</v>
+        <v>124.047</v>
       </c>
       <c r="G78">
         <v>16.6</v>
@@ -7683,28 +7683,28 @@
         <v>23.36666666666667</v>
       </c>
       <c r="M78">
-        <v>8.803148400000003</v>
+        <v>8.918979300000002</v>
       </c>
       <c r="N78">
-        <v>14.56351826666666</v>
+        <v>14.44768736666667</v>
       </c>
       <c r="O78">
-        <v>3.932149932</v>
+        <v>3.900875589</v>
       </c>
       <c r="P78">
-        <v>10.63136833466666</v>
+        <v>10.54681177766667</v>
       </c>
       <c r="Q78">
-        <v>11.93136833466667</v>
+        <v>11.84681177766667</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.390492661446424</v>
+        <v>0.4042574391786338</v>
       </c>
       <c r="T78">
-        <v>4.129329265286221</v>
+        <v>4.294227755672587</v>
       </c>
       <c r="U78">
         <v>0.07190000000000001</v>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>2.65435337505689</v>
+        <v>2.619881253302904</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1333942010110858</v>
+        <v>0.1331800432750298</v>
       </c>
       <c r="C79">
-        <v>52.4819406291958</v>
+        <v>51.26290678727122</v>
       </c>
       <c r="D79">
-        <v>159.9289406291958</v>
+        <v>160.3209067872712</v>
       </c>
       <c r="E79">
-        <v>8.547000000000011</v>
+        <v>10.158</v>
       </c>
       <c r="F79">
-        <v>124.047</v>
+        <v>125.658</v>
       </c>
       <c r="G79">
         <v>16.6</v>
@@ -7765,28 +7765,28 @@
         <v>23.36666666666667</v>
       </c>
       <c r="M79">
-        <v>8.918979300000002</v>
+        <v>9.034810200000003</v>
       </c>
       <c r="N79">
-        <v>14.44768736666667</v>
+        <v>14.33185646666666</v>
       </c>
       <c r="O79">
-        <v>3.900875589</v>
+        <v>3.869601246</v>
       </c>
       <c r="P79">
-        <v>10.54681177766667</v>
+        <v>10.46225522066666</v>
       </c>
       <c r="Q79">
-        <v>11.84681177766667</v>
+        <v>11.76225522066667</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.4042574391786338</v>
+        <v>0.4192735603410447</v>
       </c>
       <c r="T79">
-        <v>4.294227755672587</v>
+        <v>4.474117017912261</v>
       </c>
       <c r="U79">
         <v>0.07190000000000001</v>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>2.619881253302904</v>
+        <v>2.586293032106713</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1331800432750298</v>
+        <v>0.1329658855389739</v>
       </c>
       <c r="C80">
-        <v>51.26290678727122</v>
+        <v>50.04579898750187</v>
       </c>
       <c r="D80">
-        <v>160.3209067872712</v>
+        <v>160.7147989875019</v>
       </c>
       <c r="E80">
-        <v>10.158</v>
+        <v>11.76900000000001</v>
       </c>
       <c r="F80">
-        <v>125.658</v>
+        <v>127.269</v>
       </c>
       <c r="G80">
         <v>16.6</v>
@@ -7847,28 +7847,28 @@
         <v>23.36666666666667</v>
       </c>
       <c r="M80">
-        <v>9.034810200000003</v>
+        <v>9.150641100000001</v>
       </c>
       <c r="N80">
-        <v>14.33185646666666</v>
+        <v>14.21602556666667</v>
       </c>
       <c r="O80">
-        <v>3.869601246</v>
+        <v>3.838326903</v>
       </c>
       <c r="P80">
-        <v>10.46225522066666</v>
+        <v>10.37769866366667</v>
       </c>
       <c r="Q80">
-        <v>11.76225522066667</v>
+        <v>11.67769866366667</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.4192735603410447</v>
+        <v>0.4357197882808279</v>
       </c>
       <c r="T80">
-        <v>4.474117017912261</v>
+        <v>4.671138590841426</v>
       </c>
       <c r="U80">
         <v>0.07190000000000001</v>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>2.586293032106713</v>
+        <v>2.55355514562435</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1329658855389739</v>
+        <v>0.1327517278029179</v>
       </c>
       <c r="C81">
-        <v>50.04579898750187</v>
+        <v>48.83063146112298</v>
       </c>
       <c r="D81">
-        <v>160.7147989875019</v>
+        <v>161.110631461123</v>
       </c>
       <c r="E81">
-        <v>11.76900000000001</v>
+        <v>13.38000000000001</v>
       </c>
       <c r="F81">
-        <v>127.269</v>
+        <v>128.88</v>
       </c>
       <c r="G81">
         <v>16.6</v>
@@ -7929,28 +7929,28 @@
         <v>23.36666666666667</v>
       </c>
       <c r="M81">
-        <v>9.150641100000001</v>
+        <v>9.266472000000002</v>
       </c>
       <c r="N81">
-        <v>14.21602556666667</v>
+        <v>14.10019466666667</v>
       </c>
       <c r="O81">
-        <v>3.838326903</v>
+        <v>3.80705256</v>
       </c>
       <c r="P81">
-        <v>10.37769866366667</v>
+        <v>10.29314210666666</v>
       </c>
       <c r="Q81">
-        <v>11.67769866366667</v>
+        <v>11.59314210666667</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.4357197882808279</v>
+        <v>0.4538106390145895</v>
       </c>
       <c r="T81">
-        <v>4.671138590841426</v>
+        <v>4.887862321063508</v>
       </c>
       <c r="U81">
         <v>0.07190000000000001</v>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>2.55355514562435</v>
+        <v>2.521635706304045</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1327517278029179</v>
+        <v>0.1348436400668619</v>
       </c>
       <c r="C82">
-        <v>48.83063146112298</v>
+        <v>43.43464125236451</v>
       </c>
       <c r="D82">
-        <v>161.110631461123</v>
+        <v>157.3256412523645</v>
       </c>
       <c r="E82">
-        <v>13.38000000000001</v>
+        <v>14.991</v>
       </c>
       <c r="F82">
-        <v>128.88</v>
+        <v>130.491</v>
       </c>
       <c r="G82">
         <v>16.6</v>
@@ -8011,45 +8011,45 @@
         <v>23.36666666666667</v>
       </c>
       <c r="M82">
-        <v>9.266472000000002</v>
+        <v>9.891217800000002</v>
       </c>
       <c r="N82">
-        <v>14.10019466666667</v>
+        <v>13.47544886666667</v>
       </c>
       <c r="O82">
-        <v>3.80705256</v>
+        <v>3.638371194</v>
       </c>
       <c r="P82">
-        <v>10.29314210666666</v>
+        <v>9.837077672666666</v>
       </c>
       <c r="Q82">
-        <v>11.59314210666667</v>
+        <v>11.13707767266667</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.4538106390145895</v>
+        <v>0.4738057898255891</v>
       </c>
       <c r="T82">
-        <v>4.887862321063508</v>
+        <v>5.127399075519494</v>
       </c>
       <c r="U82">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V82">
         <v>0.27</v>
       </c>
       <c r="W82">
-        <v>0.05248700000000001</v>
+        <v>0.055334</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y82">
-        <v>2.521635706304045</v>
+        <v>2.362364992778408</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1348436400668619</v>
+        <v>0.1346579523308059</v>
       </c>
       <c r="C83">
-        <v>43.43464125236451</v>
+        <v>42.15240689889825</v>
       </c>
       <c r="D83">
-        <v>157.3256412523645</v>
+        <v>157.6544068988983</v>
       </c>
       <c r="E83">
-        <v>14.991</v>
+        <v>16.60200000000002</v>
       </c>
       <c r="F83">
-        <v>130.491</v>
+        <v>132.102</v>
       </c>
       <c r="G83">
         <v>16.6</v>
@@ -8093,28 +8093,28 @@
         <v>23.36666666666667</v>
       </c>
       <c r="M83">
-        <v>9.891217800000002</v>
+        <v>10.0133316</v>
       </c>
       <c r="N83">
-        <v>13.47544886666667</v>
+        <v>13.35333506666666</v>
       </c>
       <c r="O83">
-        <v>3.638371194</v>
+        <v>3.605400468</v>
       </c>
       <c r="P83">
-        <v>9.837077672666666</v>
+        <v>9.747934598666665</v>
       </c>
       <c r="Q83">
-        <v>11.13707767266667</v>
+        <v>11.04793459866667</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.4738057898255891</v>
+        <v>0.4960226240600331</v>
       </c>
       <c r="T83">
-        <v>5.127399075519494</v>
+        <v>5.393551024915034</v>
       </c>
       <c r="U83">
         <v>0.07580000000000001</v>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>2.362364992778408</v>
+        <v>2.333555663598184</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1346579523308059</v>
+        <v>0.13447226459475</v>
       </c>
       <c r="C84">
-        <v>42.15240689889825</v>
+        <v>40.87154947538585</v>
       </c>
       <c r="D84">
-        <v>157.6544068988983</v>
+        <v>157.9845494753859</v>
       </c>
       <c r="E84">
-        <v>16.60200000000002</v>
+        <v>18.21300000000001</v>
       </c>
       <c r="F84">
-        <v>132.102</v>
+        <v>133.713</v>
       </c>
       <c r="G84">
         <v>16.6</v>
@@ -8175,28 +8175,28 @@
         <v>23.36666666666667</v>
       </c>
       <c r="M84">
-        <v>10.0133316</v>
+        <v>10.1354454</v>
       </c>
       <c r="N84">
-        <v>13.35333506666666</v>
+        <v>13.23122126666667</v>
       </c>
       <c r="O84">
-        <v>3.605400468</v>
+        <v>3.572429742</v>
       </c>
       <c r="P84">
-        <v>9.747934598666665</v>
+        <v>9.658791524666665</v>
       </c>
       <c r="Q84">
-        <v>11.04793459866667</v>
+        <v>10.95879152466667</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.4960226240600331</v>
+        <v>0.5208532034985295</v>
       </c>
       <c r="T84">
-        <v>5.393551024915034</v>
+        <v>5.691014968357109</v>
       </c>
       <c r="U84">
         <v>0.07580000000000001</v>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>2.333555663598184</v>
+        <v>2.305440535121097</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.13447226459475</v>
+        <v>0.134286576858694</v>
       </c>
       <c r="C85">
-        <v>40.87154947538585</v>
+        <v>39.59207765022703</v>
       </c>
       <c r="D85">
-        <v>157.9845494753859</v>
+        <v>158.3160776502271</v>
       </c>
       <c r="E85">
-        <v>18.21300000000001</v>
+        <v>19.82400000000003</v>
       </c>
       <c r="F85">
-        <v>133.713</v>
+        <v>135.324</v>
       </c>
       <c r="G85">
         <v>16.6</v>
@@ -8257,28 +8257,28 @@
         <v>23.36666666666667</v>
       </c>
       <c r="M85">
-        <v>10.1354454</v>
+        <v>10.2575592</v>
       </c>
       <c r="N85">
-        <v>13.23122126666667</v>
+        <v>13.10910746666666</v>
       </c>
       <c r="O85">
-        <v>3.572429742</v>
+        <v>3.539459015999999</v>
       </c>
       <c r="P85">
-        <v>9.658791524666665</v>
+        <v>9.569648450666664</v>
       </c>
       <c r="Q85">
-        <v>10.95879152466667</v>
+        <v>10.86964845066666</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.5208532034985295</v>
+        <v>0.5487876053668378</v>
       </c>
       <c r="T85">
-        <v>5.691014968357109</v>
+        <v>6.025661904729443</v>
       </c>
       <c r="U85">
         <v>0.07580000000000001</v>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>2.305440535121097</v>
+        <v>2.277994814464893</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.134286576858694</v>
+        <v>0.134100889122638</v>
       </c>
       <c r="C86">
-        <v>39.59207765022705</v>
+        <v>38.31400016473654</v>
       </c>
       <c r="D86">
-        <v>158.3160776502271</v>
+        <v>158.6490001647365</v>
       </c>
       <c r="E86">
-        <v>19.824</v>
+        <v>21.43499999999999</v>
       </c>
       <c r="F86">
-        <v>135.324</v>
+        <v>136.935</v>
       </c>
       <c r="G86">
         <v>16.6</v>
@@ -8339,28 +8339,28 @@
         <v>23.36666666666667</v>
       </c>
       <c r="M86">
-        <v>10.2575592</v>
+        <v>10.379673</v>
       </c>
       <c r="N86">
-        <v>13.10910746666667</v>
+        <v>12.98699366666667</v>
       </c>
       <c r="O86">
-        <v>3.539459016</v>
+        <v>3.50648829</v>
       </c>
       <c r="P86">
-        <v>9.569648450666666</v>
+        <v>9.480505376666667</v>
       </c>
       <c r="Q86">
-        <v>10.86964845066667</v>
+        <v>10.78050537666667</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.5487876053668375</v>
+        <v>0.5804465941509201</v>
       </c>
       <c r="T86">
-        <v>6.025661904729438</v>
+        <v>6.404928432618082</v>
       </c>
       <c r="U86">
         <v>0.07580000000000001</v>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>2.277994814464894</v>
+        <v>2.251194875471189</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.134100889122638</v>
+        <v>0.1339152013865821</v>
       </c>
       <c r="C87">
-        <v>38.31400016473654</v>
+        <v>37.03732583391235</v>
       </c>
       <c r="D87">
-        <v>158.6490001647365</v>
+        <v>158.9833258339124</v>
       </c>
       <c r="E87">
-        <v>21.43499999999999</v>
+        <v>23.04600000000001</v>
       </c>
       <c r="F87">
-        <v>136.935</v>
+        <v>138.546</v>
       </c>
       <c r="G87">
         <v>16.6</v>
@@ -8421,28 +8421,28 @@
         <v>23.36666666666667</v>
       </c>
       <c r="M87">
-        <v>10.379673</v>
+        <v>10.5017868</v>
       </c>
       <c r="N87">
-        <v>12.98699366666667</v>
+        <v>12.86487986666666</v>
       </c>
       <c r="O87">
-        <v>3.50648829</v>
+        <v>3.473517563999999</v>
       </c>
       <c r="P87">
-        <v>9.480505376666667</v>
+        <v>9.391362302666664</v>
       </c>
       <c r="Q87">
-        <v>10.78050537666667</v>
+        <v>10.69136230266666</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.5804465941509201</v>
+        <v>0.6166282956184432</v>
       </c>
       <c r="T87">
-        <v>6.404928432618082</v>
+        <v>6.838375893062246</v>
       </c>
       <c r="U87">
         <v>0.07580000000000001</v>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>2.251194875471189</v>
+        <v>2.225018190872686</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1339152013865821</v>
+        <v>0.1337295136505261</v>
       </c>
       <c r="C88">
-        <v>37.03732583391235</v>
+        <v>35.76206354721396</v>
       </c>
       <c r="D88">
-        <v>158.9833258339124</v>
+        <v>159.319063547214</v>
       </c>
       <c r="E88">
-        <v>23.04600000000001</v>
+        <v>24.657</v>
       </c>
       <c r="F88">
-        <v>138.546</v>
+        <v>140.157</v>
       </c>
       <c r="G88">
         <v>16.6</v>
@@ -8503,28 +8503,28 @@
         <v>23.36666666666667</v>
       </c>
       <c r="M88">
-        <v>10.5017868</v>
+        <v>10.6239006</v>
       </c>
       <c r="N88">
-        <v>12.86487986666666</v>
+        <v>12.74276606666666</v>
       </c>
       <c r="O88">
-        <v>3.473517563999999</v>
+        <v>3.440546837999999</v>
       </c>
       <c r="P88">
-        <v>9.391362302666664</v>
+        <v>9.302219228666665</v>
       </c>
       <c r="Q88">
-        <v>10.69136230266666</v>
+        <v>10.60221922866667</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.6166282956184432</v>
+        <v>0.6583764126963546</v>
       </c>
       <c r="T88">
-        <v>6.838375893062246</v>
+        <v>7.338507578190129</v>
       </c>
       <c r="U88">
         <v>0.07580000000000001</v>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>2.225018190872686</v>
+        <v>2.199443269138518</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1337295136505261</v>
+        <v>0.1335438259144701</v>
       </c>
       <c r="C89">
-        <v>35.76206354721396</v>
+        <v>34.48822226934982</v>
       </c>
       <c r="D89">
-        <v>159.319063547214</v>
+        <v>159.6562222693499</v>
       </c>
       <c r="E89">
-        <v>24.657</v>
+        <v>26.26800000000001</v>
       </c>
       <c r="F89">
-        <v>140.157</v>
+        <v>141.768</v>
       </c>
       <c r="G89">
         <v>16.6</v>
@@ -8585,28 +8585,28 @@
         <v>23.36666666666667</v>
       </c>
       <c r="M89">
-        <v>10.6239006</v>
+        <v>10.7460144</v>
       </c>
       <c r="N89">
-        <v>12.74276606666666</v>
+        <v>12.62065226666666</v>
       </c>
       <c r="O89">
-        <v>3.440546837999999</v>
+        <v>3.407576111999999</v>
       </c>
       <c r="P89">
-        <v>9.302219228666665</v>
+        <v>9.213076154666664</v>
       </c>
       <c r="Q89">
-        <v>10.60221922866667</v>
+        <v>10.51307615466667</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.6583764126963546</v>
+        <v>0.7070825492872512</v>
       </c>
       <c r="T89">
-        <v>7.338507578190129</v>
+        <v>7.921994544172659</v>
       </c>
       <c r="U89">
         <v>0.07580000000000001</v>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>2.199443269138518</v>
+        <v>2.17444959562558</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1335438259144701</v>
+        <v>0.1333581381784142</v>
       </c>
       <c r="C90">
-        <v>34.48822226934982</v>
+        <v>33.2158110410758</v>
       </c>
       <c r="D90">
-        <v>159.6562222693499</v>
+        <v>159.9948110410758</v>
       </c>
       <c r="E90">
-        <v>26.26800000000001</v>
+        <v>27.879</v>
       </c>
       <c r="F90">
-        <v>141.768</v>
+        <v>143.379</v>
       </c>
       <c r="G90">
         <v>16.6</v>
@@ -8667,28 +8667,28 @@
         <v>23.36666666666667</v>
       </c>
       <c r="M90">
-        <v>10.7460144</v>
+        <v>10.8681282</v>
       </c>
       <c r="N90">
-        <v>12.62065226666666</v>
+        <v>12.49853846666666</v>
       </c>
       <c r="O90">
-        <v>3.407576111999999</v>
+        <v>3.374605385999999</v>
       </c>
       <c r="P90">
-        <v>9.213076154666664</v>
+        <v>9.123933080666665</v>
       </c>
       <c r="Q90">
-        <v>10.51307615466667</v>
+        <v>10.42393308066667</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.7070825492872512</v>
+        <v>0.7646443470764925</v>
       </c>
       <c r="T90">
-        <v>7.921994544172659</v>
+        <v>8.611570049424738</v>
       </c>
       <c r="U90">
         <v>0.07580000000000001</v>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>2.17444959562558</v>
+        <v>2.150017577697203</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1333581381784142</v>
+        <v>0.1331724504423582</v>
       </c>
       <c r="C91">
-        <v>33.2158110410758</v>
+        <v>31.94483898000286</v>
       </c>
       <c r="D91">
-        <v>159.9948110410758</v>
+        <v>160.3348389800029</v>
       </c>
       <c r="E91">
-        <v>27.879</v>
+        <v>29.49000000000002</v>
       </c>
       <c r="F91">
-        <v>143.379</v>
+        <v>144.99</v>
       </c>
       <c r="G91">
         <v>16.6</v>
@@ -8749,28 +8749,28 @@
         <v>23.36666666666667</v>
       </c>
       <c r="M91">
-        <v>10.8681282</v>
+        <v>10.990242</v>
       </c>
       <c r="N91">
-        <v>12.49853846666666</v>
+        <v>12.37642466666666</v>
       </c>
       <c r="O91">
-        <v>3.374605385999999</v>
+        <v>3.341634659999999</v>
       </c>
       <c r="P91">
-        <v>9.123933080666665</v>
+        <v>9.034790006666665</v>
       </c>
       <c r="Q91">
-        <v>10.42393308066667</v>
+        <v>10.33479000666667</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.7646443470764925</v>
+        <v>0.8337185044235821</v>
       </c>
       <c r="T91">
-        <v>8.611570049424738</v>
+        <v>9.439060655727234</v>
       </c>
       <c r="U91">
         <v>0.07580000000000001</v>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>2.150017577697203</v>
+        <v>2.126128493500567</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1331724504423582</v>
+        <v>0.1329867627063022</v>
       </c>
       <c r="C92">
-        <v>31.94483898000286</v>
+        <v>30.67531528141561</v>
       </c>
       <c r="D92">
-        <v>160.3348389800029</v>
+        <v>160.6763152814156</v>
       </c>
       <c r="E92">
-        <v>29.49000000000002</v>
+        <v>31.10100000000001</v>
       </c>
       <c r="F92">
-        <v>144.99</v>
+        <v>146.601</v>
       </c>
       <c r="G92">
         <v>16.6</v>
@@ -8831,28 +8831,28 @@
         <v>23.36666666666667</v>
       </c>
       <c r="M92">
-        <v>10.990242</v>
+        <v>11.1123558</v>
       </c>
       <c r="N92">
-        <v>12.37642466666666</v>
+        <v>12.25431086666666</v>
       </c>
       <c r="O92">
-        <v>3.341634659999999</v>
+        <v>3.308663934</v>
       </c>
       <c r="P92">
-        <v>9.034790006666665</v>
+        <v>8.945646932666664</v>
       </c>
       <c r="Q92">
-        <v>10.33479000666667</v>
+        <v>10.24564693266666</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.8337185044235821</v>
+        <v>0.9181424745144696</v>
       </c>
       <c r="T92">
-        <v>9.439060655727234</v>
+        <v>10.45043806343029</v>
       </c>
       <c r="U92">
         <v>0.07580000000000001</v>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>2.126128493500567</v>
+        <v>2.10276444412144</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1329867627063022</v>
+        <v>0.1328010749702463</v>
       </c>
       <c r="C93">
-        <v>30.67531528141561</v>
+        <v>29.40724921910106</v>
       </c>
       <c r="D93">
-        <v>160.6763152814156</v>
+        <v>161.0192492191011</v>
       </c>
       <c r="E93">
-        <v>31.10100000000001</v>
+        <v>32.712</v>
       </c>
       <c r="F93">
-        <v>146.601</v>
+        <v>148.212</v>
       </c>
       <c r="G93">
         <v>16.6</v>
@@ -8913,28 +8913,28 @@
         <v>23.36666666666667</v>
       </c>
       <c r="M93">
-        <v>11.1123558</v>
+        <v>11.2344696</v>
       </c>
       <c r="N93">
-        <v>12.25431086666666</v>
+        <v>12.13219706666666</v>
       </c>
       <c r="O93">
-        <v>3.308663934</v>
+        <v>3.275693208</v>
       </c>
       <c r="P93">
-        <v>8.945646932666664</v>
+        <v>8.856503858666665</v>
       </c>
       <c r="Q93">
-        <v>10.24564693266666</v>
+        <v>10.15650385866667</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.9181424745144696</v>
+        <v>1.023672437128079</v>
       </c>
       <c r="T93">
-        <v>10.45043806343029</v>
+        <v>11.7146598230591</v>
       </c>
       <c r="U93">
         <v>0.07580000000000001</v>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>2.10276444412144</v>
+        <v>2.079908308859251</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1328010749702463</v>
+        <v>0.1326153872341903</v>
       </c>
       <c r="C94">
-        <v>29.40724921910106</v>
+        <v>28.1406501461887</v>
       </c>
       <c r="D94">
-        <v>161.0192492191011</v>
+        <v>161.3636501461887</v>
       </c>
       <c r="E94">
-        <v>32.712</v>
+        <v>34.32300000000002</v>
       </c>
       <c r="F94">
-        <v>148.212</v>
+        <v>149.823</v>
       </c>
       <c r="G94">
         <v>16.6</v>
@@ -8995,28 +8995,28 @@
         <v>23.36666666666667</v>
       </c>
       <c r="M94">
-        <v>11.2344696</v>
+        <v>11.3565834</v>
       </c>
       <c r="N94">
-        <v>12.13219706666666</v>
+        <v>12.01008326666666</v>
       </c>
       <c r="O94">
-        <v>3.275693208</v>
+        <v>3.242722482</v>
       </c>
       <c r="P94">
-        <v>8.856503858666665</v>
+        <v>8.767360784666664</v>
       </c>
       <c r="Q94">
-        <v>10.15650385866667</v>
+        <v>10.06736078466666</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>1.023672437128079</v>
+        <v>1.159353817631291</v>
       </c>
       <c r="T94">
-        <v>11.7146598230591</v>
+        <v>13.34008779972472</v>
       </c>
       <c r="U94">
         <v>0.07580000000000001</v>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>2.079908308859251</v>
+        <v>2.057543703387646</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1326153872341903</v>
+        <v>0.1324296994981344</v>
       </c>
       <c r="C95">
-        <v>28.1406501461887</v>
+        <v>26.87552749600007</v>
       </c>
       <c r="D95">
-        <v>161.3636501461887</v>
+        <v>161.7095274960001</v>
       </c>
       <c r="E95">
-        <v>34.32300000000002</v>
+        <v>35.93400000000001</v>
       </c>
       <c r="F95">
-        <v>149.823</v>
+        <v>151.434</v>
       </c>
       <c r="G95">
         <v>16.6</v>
@@ -9077,28 +9077,28 @@
         <v>23.36666666666667</v>
       </c>
       <c r="M95">
-        <v>11.3565834</v>
+        <v>11.4786972</v>
       </c>
       <c r="N95">
-        <v>12.01008326666666</v>
+        <v>11.88796946666666</v>
       </c>
       <c r="O95">
-        <v>3.242722482</v>
+        <v>3.209751756</v>
       </c>
       <c r="P95">
-        <v>8.767360784666664</v>
+        <v>8.678217710666665</v>
       </c>
       <c r="Q95">
-        <v>10.06736078466666</v>
+        <v>9.978217710666666</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>1.159353817631291</v>
+        <v>1.340262324968907</v>
       </c>
       <c r="T95">
-        <v>13.34008779972472</v>
+        <v>15.50732510194555</v>
       </c>
       <c r="U95">
         <v>0.07580000000000001</v>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>2.057543703387646</v>
+        <v>2.035654940585649</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1324296994981344</v>
+        <v>0.1322440117620784</v>
       </c>
       <c r="C96">
-        <v>26.87552749600007</v>
+        <v>25.61189078291068</v>
       </c>
       <c r="D96">
-        <v>161.7095274960001</v>
+        <v>162.0568907829107</v>
       </c>
       <c r="E96">
-        <v>35.93400000000001</v>
+        <v>37.54500000000003</v>
       </c>
       <c r="F96">
-        <v>151.434</v>
+        <v>153.045</v>
       </c>
       <c r="G96">
         <v>16.6</v>
@@ -9159,28 +9159,28 @@
         <v>23.36666666666667</v>
       </c>
       <c r="M96">
-        <v>11.4786972</v>
+        <v>11.600811</v>
       </c>
       <c r="N96">
-        <v>11.88796946666666</v>
+        <v>11.76585566666666</v>
       </c>
       <c r="O96">
-        <v>3.209751756</v>
+        <v>3.176781029999999</v>
       </c>
       <c r="P96">
-        <v>8.678217710666665</v>
+        <v>8.589074636666664</v>
       </c>
       <c r="Q96">
-        <v>9.978217710666666</v>
+        <v>9.889074636666665</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.340262324968907</v>
+        <v>1.59353423524157</v>
       </c>
       <c r="T96">
-        <v>15.50732510194555</v>
+        <v>18.54145732505471</v>
       </c>
       <c r="U96">
         <v>0.07580000000000001</v>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>2.035654940585649</v>
+        <v>2.014226993842643</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1322440117620784</v>
+        <v>0.1420096840260224</v>
       </c>
       <c r="C97">
-        <v>25.61189078291068</v>
+        <v>7.551460566804536</v>
       </c>
       <c r="D97">
-        <v>162.0568907829107</v>
+        <v>145.6074605668046</v>
       </c>
       <c r="E97">
-        <v>37.54500000000003</v>
+        <v>39.15600000000002</v>
       </c>
       <c r="F97">
-        <v>153.045</v>
+        <v>154.656</v>
       </c>
       <c r="G97">
         <v>16.6</v>
@@ -9241,45 +9241,45 @@
         <v>23.36666666666667</v>
       </c>
       <c r="M97">
-        <v>11.600811</v>
+        <v>13.91904</v>
       </c>
       <c r="N97">
-        <v>11.76585566666666</v>
+        <v>9.447626666666665</v>
       </c>
       <c r="O97">
-        <v>3.176781029999999</v>
+        <v>2.5508592</v>
       </c>
       <c r="P97">
-        <v>8.589074636666664</v>
+        <v>6.896767466666665</v>
       </c>
       <c r="Q97">
-        <v>9.889074636666665</v>
+        <v>8.196767466666666</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.59353423524157</v>
+        <v>1.973442100650564</v>
       </c>
       <c r="T97">
-        <v>18.54145732505471</v>
+        <v>23.09265565971845</v>
       </c>
       <c r="U97">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V97">
         <v>0.27</v>
       </c>
       <c r="W97">
-        <v>0.055334</v>
+        <v>0.06569999999999999</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y97">
-        <v>2.014226993842643</v>
+        <v>1.678755622993156</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1420096840260224</v>
+        <v>0.1419276562899664</v>
       </c>
       <c r="C98">
-        <v>7.551460566804565</v>
+        <v>6.064710452884441</v>
       </c>
       <c r="D98">
-        <v>145.6074605668046</v>
+        <v>145.7317104528845</v>
       </c>
       <c r="E98">
-        <v>39.15599999999999</v>
+        <v>40.76700000000001</v>
       </c>
       <c r="F98">
-        <v>154.656</v>
+        <v>156.267</v>
       </c>
       <c r="G98">
         <v>16.6</v>
@@ -9323,28 +9323,28 @@
         <v>23.36666666666667</v>
       </c>
       <c r="M98">
-        <v>13.91904</v>
+        <v>14.06403</v>
       </c>
       <c r="N98">
-        <v>9.447626666666666</v>
+        <v>9.302636666666665</v>
       </c>
       <c r="O98">
-        <v>2.5508592</v>
+        <v>2.511711899999999</v>
       </c>
       <c r="P98">
-        <v>6.896767466666667</v>
+        <v>6.790924766666665</v>
       </c>
       <c r="Q98">
-        <v>8.196767466666667</v>
+        <v>8.090924766666665</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.973442100650559</v>
+        <v>2.606621876332212</v>
       </c>
       <c r="T98">
-        <v>23.09265565971839</v>
+        <v>30.67798621749126</v>
       </c>
       <c r="U98">
         <v>0.09</v>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>1.678755622993157</v>
+        <v>1.661448863993227</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1419276562899664</v>
+        <v>0.1418456285539105</v>
       </c>
       <c r="C99">
-        <v>6.064710452884441</v>
+        <v>4.578172570109302</v>
       </c>
       <c r="D99">
-        <v>145.7317104528845</v>
+        <v>145.8561725701093</v>
       </c>
       <c r="E99">
-        <v>40.76700000000001</v>
+        <v>42.378</v>
       </c>
       <c r="F99">
-        <v>156.267</v>
+        <v>157.878</v>
       </c>
       <c r="G99">
         <v>16.6</v>
@@ -9405,28 +9405,28 @@
         <v>23.36666666666667</v>
       </c>
       <c r="M99">
-        <v>14.06403</v>
+        <v>14.20902</v>
       </c>
       <c r="N99">
-        <v>9.302636666666665</v>
+        <v>9.157646666666666</v>
       </c>
       <c r="O99">
-        <v>2.511711899999999</v>
+        <v>2.4725646</v>
       </c>
       <c r="P99">
-        <v>6.790924766666665</v>
+        <v>6.685082066666666</v>
       </c>
       <c r="Q99">
-        <v>8.090924766666665</v>
+        <v>7.985082066666667</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>2.606621876332212</v>
+        <v>3.87298142769552</v>
       </c>
       <c r="T99">
-        <v>30.67798621749126</v>
+        <v>45.84864733303699</v>
       </c>
       <c r="U99">
         <v>0.09</v>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>1.661448863993227</v>
+        <v>1.644495304156562</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.1418456285539105</v>
+        <v>0.1417636008178545</v>
       </c>
       <c r="C100">
-        <v>4.578172570109302</v>
+        <v>3.091847462711797</v>
       </c>
       <c r="D100">
-        <v>145.8561725701093</v>
+        <v>145.9808474627118</v>
       </c>
       <c r="E100">
-        <v>42.378</v>
+        <v>43.98900000000002</v>
       </c>
       <c r="F100">
-        <v>157.878</v>
+        <v>159.489</v>
       </c>
       <c r="G100">
         <v>16.6</v>
@@ -9487,28 +9487,28 @@
         <v>23.36666666666667</v>
       </c>
       <c r="M100">
-        <v>14.20902</v>
+        <v>14.35401</v>
       </c>
       <c r="N100">
-        <v>9.157646666666666</v>
+        <v>9.012656666666665</v>
       </c>
       <c r="O100">
-        <v>2.4725646</v>
+        <v>2.433417299999999</v>
       </c>
       <c r="P100">
-        <v>6.685082066666666</v>
+        <v>6.579239366666665</v>
       </c>
       <c r="Q100">
-        <v>7.985082066666667</v>
+        <v>7.879239366666666</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>3.87298142769552</v>
+        <v>7.672060081785444</v>
       </c>
       <c r="T100">
-        <v>45.84864733303699</v>
+        <v>91.36063067967422</v>
       </c>
       <c r="U100">
         <v>0.09</v>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>1.644495304156562</v>
+        <v>1.627884240478212</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.1417636008178545</v>
-      </c>
-      <c r="C101">
-        <v>3.091847462711797</v>
-      </c>
-      <c r="D101">
-        <v>145.9808474627118</v>
-      </c>
-      <c r="E101">
-        <v>43.98900000000002</v>
-      </c>
-      <c r="F101">
-        <v>159.489</v>
-      </c>
-      <c r="G101">
-        <v>16.6</v>
-      </c>
-      <c r="H101">
-        <v>45.6</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>24.66666666666667</v>
-      </c>
-      <c r="K101">
-        <v>1.300000000000001</v>
-      </c>
-      <c r="L101">
-        <v>23.36666666666667</v>
-      </c>
-      <c r="M101">
-        <v>14.35401</v>
-      </c>
-      <c r="N101">
-        <v>9.012656666666665</v>
-      </c>
-      <c r="O101">
-        <v>2.433417299999999</v>
-      </c>
-      <c r="P101">
-        <v>6.579239366666665</v>
-      </c>
-      <c r="Q101">
-        <v>7.879239366666666</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>7.672060081785444</v>
-      </c>
-      <c r="T101">
-        <v>91.36063067967422</v>
-      </c>
-      <c r="U101">
-        <v>0.09</v>
-      </c>
-      <c r="V101">
-        <v>0.27</v>
-      </c>
-      <c r="W101">
-        <v>0.06569999999999999</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>B3/B-</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>1.627884240478212</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
